--- a/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8BD231E-53F1-477B-9F30-D6547477FE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A2F99C-11ED-40FE-90BE-EF0C9D111364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5270,7 +5270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA00301-2FF6-4533-878B-82DA0FECC4F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA0B652E-CCE1-45C0-82C2-80892F551D54}">
   <dimension ref="B9:D191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7287,7 +7287,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730EB7E4-D14B-43F6-A32B-293B2C5EC513}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DB4A1A-EDD3-4FAD-90D4-7CDB48079C79}">
   <dimension ref="B2:D184"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A2F99C-11ED-40FE-90BE-EF0C9D111364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC6D6437-FC37-43C8-9DDA-808F10CA80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5270,7 +5270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA0B652E-CCE1-45C0-82C2-80892F551D54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57309AC4-3703-4DE2-BB23-03B5C36CFC29}">
   <dimension ref="B9:D191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7011,10 +7011,10 @@
         <v>454</v>
       </c>
       <c r="C167">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D167">
-        <v>6.2896976410000001</v>
+        <v>6.289697641356212</v>
       </c>
     </row>
     <row r="168" spans="2:4">
@@ -7022,10 +7022,10 @@
         <v>455</v>
       </c>
       <c r="C168">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D168">
-        <v>6.2896976410000001</v>
+        <v>6.289697641356212</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -7033,10 +7033,10 @@
         <v>456</v>
       </c>
       <c r="C169">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D169">
-        <v>6.2896976410000001</v>
+        <v>6.289697641356212</v>
       </c>
     </row>
     <row r="170" spans="2:4">
@@ -7044,10 +7044,10 @@
         <v>457</v>
       </c>
       <c r="C170">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D170">
-        <v>6.9349650939999998</v>
+        <v>6.9349650942374748</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -7055,10 +7055,10 @@
         <v>458</v>
       </c>
       <c r="C171">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D171">
-        <v>6.9349650939999998</v>
+        <v>6.9349650942374748</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -7066,10 +7066,10 @@
         <v>459</v>
       </c>
       <c r="C172">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D172">
-        <v>6.9349650939999998</v>
+        <v>6.9349650942374748</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -7077,10 +7077,10 @@
         <v>460</v>
       </c>
       <c r="C173">
-        <v>47.48699027</v>
+        <v>47.486990272793413</v>
       </c>
       <c r="D173">
-        <v>6.9349650939999998</v>
+        <v>6.9349650942374748</v>
       </c>
     </row>
     <row r="174" spans="2:4">
@@ -7088,10 +7088,10 @@
         <v>461</v>
       </c>
       <c r="C174">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D174">
-        <v>7.5802325469999996</v>
+        <v>7.5802325471187393</v>
       </c>
     </row>
     <row r="175" spans="2:4">
@@ -7099,10 +7099,10 @@
         <v>462</v>
       </c>
       <c r="C175">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D175">
-        <v>7.5802325469999996</v>
+        <v>7.5802325471187393</v>
       </c>
     </row>
     <row r="176" spans="2:4">
@@ -7110,10 +7110,10 @@
         <v>463</v>
       </c>
       <c r="C176">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D176">
-        <v>7.5802325469999996</v>
+        <v>7.5802325471187393</v>
       </c>
     </row>
     <row r="177" spans="2:4">
@@ -7121,10 +7121,10 @@
         <v>464</v>
       </c>
       <c r="C177">
-        <v>47.48699027</v>
+        <v>47.486990272793413</v>
       </c>
       <c r="D177">
-        <v>7.5802325469999996</v>
+        <v>7.5802325471187393</v>
       </c>
     </row>
     <row r="178" spans="2:4">
@@ -7132,10 +7132,10 @@
         <v>465</v>
       </c>
       <c r="C178">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D178">
-        <v>8.2255000000000003</v>
+        <v>8.225500000000002</v>
       </c>
     </row>
     <row r="179" spans="2:4">
@@ -7143,10 +7143,10 @@
         <v>466</v>
       </c>
       <c r="C179">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D179">
-        <v>8.2255000000000003</v>
+        <v>8.225500000000002</v>
       </c>
     </row>
     <row r="180" spans="2:4">
@@ -7154,10 +7154,10 @@
         <v>467</v>
       </c>
       <c r="C180">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D180">
-        <v>8.2255000000000003</v>
+        <v>8.225500000000002</v>
       </c>
     </row>
     <row r="181" spans="2:4">
@@ -7165,10 +7165,10 @@
         <v>468</v>
       </c>
       <c r="C181">
-        <v>47.48699027</v>
+        <v>47.486990272793413</v>
       </c>
       <c r="D181">
-        <v>8.2255000000000003</v>
+        <v>8.225500000000002</v>
       </c>
     </row>
     <row r="182" spans="2:4">
@@ -7176,10 +7176,10 @@
         <v>469</v>
       </c>
       <c r="C182">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D182">
-        <v>8.8707674529999991</v>
+        <v>8.8707674528812674</v>
       </c>
     </row>
     <row r="183" spans="2:4">
@@ -7187,10 +7187,10 @@
         <v>470</v>
       </c>
       <c r="C183">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D183">
-        <v>8.8707674529999991</v>
+        <v>8.8707674528812674</v>
       </c>
     </row>
     <row r="184" spans="2:4">
@@ -7198,10 +7198,10 @@
         <v>471</v>
       </c>
       <c r="C184">
-        <v>47.48699027</v>
+        <v>47.486990272793413</v>
       </c>
       <c r="D184">
-        <v>8.8707674529999991</v>
+        <v>8.8707674528812674</v>
       </c>
     </row>
     <row r="185" spans="2:4">
@@ -7209,10 +7209,10 @@
         <v>472</v>
       </c>
       <c r="C185">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D185">
-        <v>9.5160349059999998</v>
+        <v>9.5160349057625293</v>
       </c>
     </row>
     <row r="186" spans="2:4">
@@ -7220,10 +7220,10 @@
         <v>473</v>
       </c>
       <c r="C186">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D186">
-        <v>9.5160349059999998</v>
+        <v>9.5160349057625293</v>
       </c>
     </row>
     <row r="187" spans="2:4">
@@ -7231,10 +7231,10 @@
         <v>474</v>
       </c>
       <c r="C187">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D187">
-        <v>9.5160349059999998</v>
+        <v>9.5160349057625293</v>
       </c>
     </row>
     <row r="188" spans="2:4">
@@ -7242,10 +7242,10 @@
         <v>475</v>
       </c>
       <c r="C188">
-        <v>47.48699027</v>
+        <v>47.486990272793413</v>
       </c>
       <c r="D188">
-        <v>9.5160349059999998</v>
+        <v>9.5160349057625293</v>
       </c>
     </row>
     <row r="189" spans="2:4">
@@ -7253,10 +7253,10 @@
         <v>476</v>
       </c>
       <c r="C189">
-        <v>46.13800973</v>
+        <v>46.138009727206594</v>
       </c>
       <c r="D189">
-        <v>10.161302360000001</v>
+        <v>10.161302358643791</v>
       </c>
     </row>
     <row r="190" spans="2:4">
@@ -7264,10 +7264,10 @@
         <v>477</v>
       </c>
       <c r="C190">
-        <v>46.587669910000002</v>
+        <v>46.587669909068872</v>
       </c>
       <c r="D190">
-        <v>10.161302360000001</v>
+        <v>10.161302358643791</v>
       </c>
     </row>
     <row r="191" spans="2:4">
@@ -7275,10 +7275,10 @@
         <v>478</v>
       </c>
       <c r="C191">
-        <v>47.037330089999998</v>
+        <v>47.037330090931135</v>
       </c>
       <c r="D191">
-        <v>10.161302360000001</v>
+        <v>10.161302358643791</v>
       </c>
     </row>
   </sheetData>
@@ -7287,7 +7287,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DB4A1A-EDD3-4FAD-90D4-7CDB48079C79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC06C61E-6B66-4FC8-9526-1932D145970C}">
   <dimension ref="B2:D184"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC6D6437-FC37-43C8-9DDA-808F10CA80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3FE111B-61E9-4B35-BEBB-358F699A353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
-    <sheet name="geolocation" sheetId="72" r:id="rId2"/>
-    <sheet name="process_map_geo" sheetId="71" r:id="rId3"/>
-    <sheet name="ScenMap" sheetId="56" r:id="rId4"/>
-    <sheet name="TS_Defs" sheetId="27" r:id="rId5"/>
-    <sheet name="TS_ratios" sheetId="68" r:id="rId6"/>
+    <sheet name="ScenMap" sheetId="56" r:id="rId2"/>
+    <sheet name="TS_Defs" sheetId="27" r:id="rId3"/>
+    <sheet name="TS_ratios" sheetId="68" r:id="rId4"/>
+    <sheet name="geolocation" sheetId="72" r:id="rId5"/>
+    <sheet name="process_map_geo" sheetId="71" r:id="rId6"/>
     <sheet name="Sankey" sheetId="69" r:id="rId7"/>
     <sheet name="PSet_MAP" sheetId="57" r:id="rId8"/>
     <sheet name="CSET_MAP" sheetId="66" r:id="rId9"/>
@@ -30,7 +30,7 @@
     <sheet name="UnitConv" sheetId="59" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TS_Defs!$A$2:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TS_Defs!$A$2:$N$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -881,9 +881,6 @@
     <t>f3d</t>
   </si>
   <si>
-    <t>~TS_Defs: Snk_attr=SANKEY Grid Flows</t>
-  </si>
-  <si>
     <t>~TS_Defs: Snk_attr=SANKEY whole system</t>
   </si>
   <si>
@@ -975,6 +972,9 @@
   </si>
   <si>
     <t>f1d</t>
+  </si>
+  <si>
+    <t>DeACT TS_Defs: Snk_attr=SANKEY Grid Flows</t>
   </si>
   <si>
     <t>grid_node</t>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -4199,7 +4199,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -4217,18 +4217,18 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5270,4040 +5270,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57309AC4-3703-4DE2-BB23-03B5C36CFC29}">
-  <dimension ref="B9:D191"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>480</v>
-      </c>
-      <c r="C10" t="s">
-        <v>481</v>
-      </c>
-      <c r="D10" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11">
-        <v>47.544890908098111</v>
-      </c>
-      <c r="D11">
-        <v>7.9712762161849238</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12">
-        <v>47.304724827935445</v>
-      </c>
-      <c r="D12">
-        <v>7.7779031530618461</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13">
-        <v>47.190849773284448</v>
-      </c>
-      <c r="D13">
-        <v>8.98591839231268</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14">
-        <v>47.178826311182746</v>
-      </c>
-      <c r="D14">
-        <v>8.9144143549561985</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15">
-        <v>47.092480331016233</v>
-      </c>
-      <c r="D15">
-        <v>7.6486786287370201</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16">
-        <v>47.075251392097968</v>
-      </c>
-      <c r="D16">
-        <v>8.2262357999999978</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17">
-        <v>46.998666392047838</v>
-      </c>
-      <c r="D17">
-        <v>9.1028854000000017</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18">
-        <v>46.948264900775179</v>
-      </c>
-      <c r="D18">
-        <v>9.4806532222174642</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19">
-        <v>46.881453574552602</v>
-      </c>
-      <c r="D19">
-        <v>8.9862021733683619</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20">
-        <v>46.810115191923131</v>
-      </c>
-      <c r="D20">
-        <v>8.0932617000000064</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" t="s">
-        <v>308</v>
-      </c>
-      <c r="C21">
-        <v>47.539986892396122</v>
-      </c>
-      <c r="D21">
-        <v>7.9955895999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" t="s">
-        <v>309</v>
-      </c>
-      <c r="C22">
-        <v>46.788975991909084</v>
-      </c>
-      <c r="D22">
-        <v>8.1290422999999965</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C23">
-        <v>46.786285291907262</v>
-      </c>
-      <c r="D23">
-        <v>9.4018789000000034</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C24">
-        <v>46.664480125407628</v>
-      </c>
-      <c r="D24">
-        <v>9.5632429943814046</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" t="s">
-        <v>312</v>
-      </c>
-      <c r="C25">
-        <v>46.655434346966651</v>
-      </c>
-      <c r="D25">
-        <v>8.5931628753479483</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" t="s">
-        <v>313</v>
-      </c>
-      <c r="C26">
-        <v>46.649952591815854</v>
-      </c>
-      <c r="D26">
-        <v>8.5784506999999994</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27">
-        <v>46.644906911551253</v>
-      </c>
-      <c r="D27">
-        <v>8.3005733260132732</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" t="s">
-        <v>315</v>
-      </c>
-      <c r="C28">
-        <v>46.623454943499027</v>
-      </c>
-      <c r="D28">
-        <v>8.5532759599539414</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" t="s">
-        <v>316</v>
-      </c>
-      <c r="C29">
-        <v>46.618279365377013</v>
-      </c>
-      <c r="D29">
-        <v>8.3074651919389026</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" t="s">
-        <v>317</v>
-      </c>
-      <c r="C30">
-        <v>46.612461191790615</v>
-      </c>
-      <c r="D30">
-        <v>8.5613045000000074</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31">
-        <v>46.581937628506168</v>
-      </c>
-      <c r="D31">
-        <v>9.6114226583534901</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" t="s">
-        <v>319</v>
-      </c>
-      <c r="C32">
-        <v>47.446856248318333</v>
-      </c>
-      <c r="D32">
-        <v>8.7203907336648729</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33">
-        <v>46.568629391760908</v>
-      </c>
-      <c r="D33">
-        <v>9.9176659999999917</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
-        <v>321</v>
-      </c>
-      <c r="C34">
-        <v>46.56229679175663</v>
-      </c>
-      <c r="D34">
-        <v>6.5602429000000066</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
-        <v>322</v>
-      </c>
-      <c r="C35">
-        <v>46.534677991737887</v>
-      </c>
-      <c r="D35">
-        <v>8.9442773999999901</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
-        <v>323</v>
-      </c>
-      <c r="C36">
-        <v>46.526125791732063</v>
-      </c>
-      <c r="D36">
-        <v>9.8856431000000047</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
-        <v>324</v>
-      </c>
-      <c r="C37">
-        <v>46.497898379860622</v>
-      </c>
-      <c r="D37">
-        <v>8.3151001429309765</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
-        <v>325</v>
-      </c>
-      <c r="C38">
-        <v>46.488751691706611</v>
-      </c>
-      <c r="D38">
-        <v>8.4733173999999973</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>326</v>
-      </c>
-      <c r="C39">
-        <v>46.484022953389079</v>
-      </c>
-      <c r="D39">
-        <v>8.345911817931027</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
-        <v>327</v>
-      </c>
-      <c r="C40">
-        <v>46.48232639170228</v>
-      </c>
-      <c r="D40">
-        <v>9.9156705000000098</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
-        <v>328</v>
-      </c>
-      <c r="C41">
-        <v>46.477333091698902</v>
-      </c>
-      <c r="D41">
-        <v>8.4126624000000021</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42">
-        <v>46.473546691696313</v>
-      </c>
-      <c r="D42">
-        <v>8.3779117000000021</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
-        <v>330</v>
-      </c>
-      <c r="C43">
-        <v>47.434850092329576</v>
-      </c>
-      <c r="D43">
-        <v>9.4308717000000009</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
-        <v>331</v>
-      </c>
-      <c r="C44">
-        <v>46.461142191687813</v>
-      </c>
-      <c r="D44">
-        <v>8.4521007999999931</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
-        <v>332</v>
-      </c>
-      <c r="C45">
-        <v>46.42086779166025</v>
-      </c>
-      <c r="D45">
-        <v>9.2172236999999928</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
-        <v>333</v>
-      </c>
-      <c r="C46">
-        <v>46.410782691653388</v>
-      </c>
-      <c r="D46">
-        <v>8.6464327000000054</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
-        <v>334</v>
-      </c>
-      <c r="C47">
-        <v>46.379313191631766</v>
-      </c>
-      <c r="D47">
-        <v>7.2856905999999926</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
-        <v>335</v>
-      </c>
-      <c r="C48">
-        <v>46.352076391613046</v>
-      </c>
-      <c r="D48">
-        <v>7.2952704999999991</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" t="s">
-        <v>336</v>
-      </c>
-      <c r="C49">
-        <v>46.335742191601824</v>
-      </c>
-      <c r="D49">
-        <v>9.515274700000008</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" t="s">
-        <v>337</v>
-      </c>
-      <c r="C50">
-        <v>46.332593945141092</v>
-      </c>
-      <c r="D50">
-        <v>8.0099601184858678</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" t="s">
-        <v>338</v>
-      </c>
-      <c r="C51">
-        <v>46.300225691577296</v>
-      </c>
-      <c r="D51">
-        <v>7.9090832000000049</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" t="s">
-        <v>339</v>
-      </c>
-      <c r="C52">
-        <v>46.265255891553082</v>
-      </c>
-      <c r="D52">
-        <v>6.8250681999999925</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" t="s">
-        <v>340</v>
-      </c>
-      <c r="C53">
-        <v>46.258617991548483</v>
-      </c>
-      <c r="D53">
-        <v>6.8503240000000041</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" t="s">
-        <v>341</v>
-      </c>
-      <c r="C54">
-        <v>47.417551492318573</v>
-      </c>
-      <c r="D54">
-        <v>8.3560802000000063</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" t="s">
-        <v>342</v>
-      </c>
-      <c r="C55">
-        <v>46.242902191537631</v>
-      </c>
-      <c r="D55">
-        <v>9.0158809000000044</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" t="s">
-        <v>343</v>
-      </c>
-      <c r="C56">
-        <v>46.238390468466378</v>
-      </c>
-      <c r="D56">
-        <v>6.0514922014978874</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" t="s">
-        <v>344</v>
-      </c>
-      <c r="C57">
-        <v>46.235914155009169</v>
-      </c>
-      <c r="D57">
-        <v>6.1174054082285867</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" t="s">
-        <v>345</v>
-      </c>
-      <c r="C58">
-        <v>46.224393391524778</v>
-      </c>
-      <c r="D58">
-        <v>6.9826246999999961</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" t="s">
-        <v>346</v>
-      </c>
-      <c r="C59">
-        <v>46.194148141506382</v>
-      </c>
-      <c r="D59">
-        <v>8.8493960000010343</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" t="s">
-        <v>347</v>
-      </c>
-      <c r="C60">
-        <v>46.186124268919009</v>
-      </c>
-      <c r="D60">
-        <v>5.994340131372339</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" t="s">
-        <v>348</v>
-      </c>
-      <c r="C61">
-        <v>46.173823141643673</v>
-      </c>
-      <c r="D61">
-        <v>8.8978103000914679</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62" t="s">
-        <v>349</v>
-      </c>
-      <c r="C62">
-        <v>46.132986991479271</v>
-      </c>
-      <c r="D62">
-        <v>8.718542699932085</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63" t="s">
-        <v>350</v>
-      </c>
-      <c r="C63">
-        <v>47.388461918063442</v>
-      </c>
-      <c r="D63">
-        <v>8.7320753615603035</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" t="s">
-        <v>351</v>
-      </c>
-      <c r="C64">
-        <v>46.119367580527111</v>
-      </c>
-      <c r="D64">
-        <v>7.0694412517776462</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" t="s">
-        <v>352</v>
-      </c>
-      <c r="C65">
-        <v>47.346106146249483</v>
-      </c>
-      <c r="D65">
-        <v>8.0436238635106729</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" t="s">
-        <v>353</v>
-      </c>
-      <c r="C66">
-        <v>47.328602392261772</v>
-      </c>
-      <c r="D66">
-        <v>9.5426184000000038</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" t="s">
-        <v>354</v>
-      </c>
-      <c r="C67">
-        <v>46.974388444635309</v>
-      </c>
-      <c r="D67">
-        <v>7.1904948515457114</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" t="s">
-        <v>355</v>
-      </c>
-      <c r="C68">
-        <v>46.804956344676071</v>
-      </c>
-      <c r="D68">
-        <v>10.332156238823757</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" t="s">
-        <v>356</v>
-      </c>
-      <c r="C69">
-        <v>47.412318641275661</v>
-      </c>
-      <c r="D69">
-        <v>8.5715564719984449</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" t="s">
-        <v>357</v>
-      </c>
-      <c r="C70">
-        <v>46.675294830039618</v>
-      </c>
-      <c r="D70">
-        <v>8.7674518660095799</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" t="s">
-        <v>358</v>
-      </c>
-      <c r="C71">
-        <v>47.271158280917277</v>
-      </c>
-      <c r="D71">
-        <v>8.4332838059847646</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" t="s">
-        <v>359</v>
-      </c>
-      <c r="C72">
-        <v>46.592025463687065</v>
-      </c>
-      <c r="D72">
-        <v>8.3231337258397549</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" t="s">
-        <v>360</v>
-      </c>
-      <c r="C73">
-        <v>47.520027177779937</v>
-      </c>
-      <c r="D73">
-        <v>7.6725301685729344</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" t="s">
-        <v>361</v>
-      </c>
-      <c r="C74">
-        <v>46.410514012428273</v>
-      </c>
-      <c r="D74">
-        <v>8.5287472013709298</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" t="s">
-        <v>362</v>
-      </c>
-      <c r="C75">
-        <v>46.972086567773282</v>
-      </c>
-      <c r="D75">
-        <v>7.282299486401616</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" t="s">
-        <v>363</v>
-      </c>
-      <c r="C76">
-        <v>46.557357312705733</v>
-      </c>
-      <c r="D76">
-        <v>6.6139061630111931</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77">
-        <v>47.378758073068163</v>
-      </c>
-      <c r="D77">
-        <v>8.6247814788577859</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="B78" t="s">
-        <v>365</v>
-      </c>
-      <c r="C78">
-        <v>46.590136747583571</v>
-      </c>
-      <c r="D78">
-        <v>9.4208498140633523</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4">
-      <c r="B79" t="s">
-        <v>366</v>
-      </c>
-      <c r="C79">
-        <v>46.766603972636261</v>
-      </c>
-      <c r="D79">
-        <v>7.1256953875579114</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80" t="s">
-        <v>367</v>
-      </c>
-      <c r="C80">
-        <v>47.337522798960869</v>
-      </c>
-      <c r="D80">
-        <v>7.2588732640160751</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" t="s">
-        <v>368</v>
-      </c>
-      <c r="C81">
-        <v>47.436744661689957</v>
-      </c>
-      <c r="D81">
-        <v>8.2162002170923429</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82" t="s">
-        <v>369</v>
-      </c>
-      <c r="C82">
-        <v>46.667290772141591</v>
-      </c>
-      <c r="D82">
-        <v>8.58387184139076</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="B83" t="s">
-        <v>370</v>
-      </c>
-      <c r="C83">
-        <v>46.366800843099547</v>
-      </c>
-      <c r="D83">
-        <v>6.1959931237841124</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="B84" t="s">
-        <v>371</v>
-      </c>
-      <c r="C84">
-        <v>46.35035364659204</v>
-      </c>
-      <c r="D84">
-        <v>8.5954343817427024</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85" t="s">
-        <v>372</v>
-      </c>
-      <c r="C85">
-        <v>46.770135591197366</v>
-      </c>
-      <c r="D85">
-        <v>8.6679070270868852</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86">
-        <v>47.185453772379887</v>
-      </c>
-      <c r="D86">
-        <v>8.1207667742378131</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87" t="s">
-        <v>374</v>
-      </c>
-      <c r="C87">
-        <v>47.23246302223221</v>
-      </c>
-      <c r="D87">
-        <v>7.6158921048685695</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" t="s">
-        <v>375</v>
-      </c>
-      <c r="C88">
-        <v>47.466610199741339</v>
-      </c>
-      <c r="D88">
-        <v>8.6524389852250962</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" t="s">
-        <v>376</v>
-      </c>
-      <c r="C89">
-        <v>47.422793373651899</v>
-      </c>
-      <c r="D89">
-        <v>8.5552286743996788</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" t="s">
-        <v>377</v>
-      </c>
-      <c r="C90">
-        <v>46.822356911553562</v>
-      </c>
-      <c r="D90">
-        <v>8.1738143462569646</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91" t="s">
-        <v>378</v>
-      </c>
-      <c r="C91">
-        <v>46.949503324895758</v>
-      </c>
-      <c r="D91">
-        <v>7.1526297591744381</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92" t="s">
-        <v>379</v>
-      </c>
-      <c r="C92">
-        <v>47.174970614196077</v>
-      </c>
-      <c r="D92">
-        <v>7.5753719705379048</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93" t="s">
-        <v>380</v>
-      </c>
-      <c r="C93">
-        <v>47.426405935677117</v>
-      </c>
-      <c r="D93">
-        <v>8.2183855607953387</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94" t="s">
-        <v>381</v>
-      </c>
-      <c r="C94">
-        <v>46.191060824589286</v>
-      </c>
-      <c r="D94">
-        <v>6.0263528951053331</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95" t="s">
-        <v>382</v>
-      </c>
-      <c r="C95">
-        <v>47.317528275969032</v>
-      </c>
-      <c r="D95">
-        <v>7.9466109226610806</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="B96" t="s">
-        <v>383</v>
-      </c>
-      <c r="C96">
-        <v>47.220028502558506</v>
-      </c>
-      <c r="D96">
-        <v>8.9741608765490568</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97" t="s">
-        <v>384</v>
-      </c>
-      <c r="C97">
-        <v>46.611103814178406</v>
-      </c>
-      <c r="D97">
-        <v>7.1119095241485661</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98" t="s">
-        <v>385</v>
-      </c>
-      <c r="C98">
-        <v>46.34885054673623</v>
-      </c>
-      <c r="D98">
-        <v>10.062555293517526</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99" t="s">
-        <v>386</v>
-      </c>
-      <c r="C99">
-        <v>46.704671298611736</v>
-      </c>
-      <c r="D99">
-        <v>9.4671012537392354</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100" t="s">
-        <v>387</v>
-      </c>
-      <c r="C100">
-        <v>46.669437648312751</v>
-      </c>
-      <c r="D100">
-        <v>9.6896555979430463</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101" t="s">
-        <v>388</v>
-      </c>
-      <c r="C101">
-        <v>46.670304209093366</v>
-      </c>
-      <c r="D101">
-        <v>7.8586620471824489</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102" t="s">
-        <v>389</v>
-      </c>
-      <c r="C102">
-        <v>46.751315983062611</v>
-      </c>
-      <c r="D102">
-        <v>9.0427987835648143</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103" t="s">
-        <v>390</v>
-      </c>
-      <c r="C103">
-        <v>46.977408013673561</v>
-      </c>
-      <c r="D103">
-        <v>9.5391741699870458</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104" t="s">
-        <v>391</v>
-      </c>
-      <c r="C104">
-        <v>46.530313679899571</v>
-      </c>
-      <c r="D104">
-        <v>9.4339157546528778</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" t="s">
-        <v>392</v>
-      </c>
-      <c r="C105">
-        <v>46.287036690944227</v>
-      </c>
-      <c r="D105">
-        <v>7.5577983541354428</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" t="s">
-        <v>393</v>
-      </c>
-      <c r="C106">
-        <v>46.083826692351948</v>
-      </c>
-      <c r="D106">
-        <v>7.956552648739204</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107" t="s">
-        <v>394</v>
-      </c>
-      <c r="C107">
-        <v>47.480988674223049</v>
-      </c>
-      <c r="D107">
-        <v>8.705750623710184</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" t="s">
-        <v>395</v>
-      </c>
-      <c r="C108">
-        <v>46.756029375970002</v>
-      </c>
-      <c r="D108">
-        <v>6.5540699286344619</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" t="s">
-        <v>396</v>
-      </c>
-      <c r="C109">
-        <v>46.185370247486951</v>
-      </c>
-      <c r="D109">
-        <v>7.2493006931109596</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" t="s">
-        <v>397</v>
-      </c>
-      <c r="C110">
-        <v>46.23792888408876</v>
-      </c>
-      <c r="D110">
-        <v>7.8746708803832934</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" t="s">
-        <v>398</v>
-      </c>
-      <c r="C111">
-        <v>46.066166211545358</v>
-      </c>
-      <c r="D111">
-        <v>6.9015998074716354</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" t="s">
-        <v>399</v>
-      </c>
-      <c r="C112">
-        <v>46.249132718394094</v>
-      </c>
-      <c r="D112">
-        <v>6.1334444282890637</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
-      <c r="B113" t="s">
-        <v>400</v>
-      </c>
-      <c r="C113">
-        <v>47.330633116676246</v>
-      </c>
-      <c r="D113">
-        <v>8.7565727921394849</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114" t="s">
-        <v>401</v>
-      </c>
-      <c r="C114">
-        <v>46.702305741170029</v>
-      </c>
-      <c r="D114">
-        <v>8.2346739749028277</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115" t="s">
-        <v>402</v>
-      </c>
-      <c r="C115">
-        <v>47.111263596162431</v>
-      </c>
-      <c r="D115">
-        <v>7.9702987999010633</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116" t="s">
-        <v>403</v>
-      </c>
-      <c r="C116">
-        <v>46.050896100089638</v>
-      </c>
-      <c r="D116">
-        <v>6.949838605733583</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
-      <c r="B117" t="s">
-        <v>404</v>
-      </c>
-      <c r="C117">
-        <v>46.778607821978291</v>
-      </c>
-      <c r="D117">
-        <v>7.5141567559463658</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118" t="s">
-        <v>405</v>
-      </c>
-      <c r="C118">
-        <v>47.559810348453667</v>
-      </c>
-      <c r="D118">
-        <v>9.0926775269382958</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" t="s">
-        <v>406</v>
-      </c>
-      <c r="C119">
-        <v>47.573740583075264</v>
-      </c>
-      <c r="D119">
-        <v>8.4736401094130844</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
-      <c r="B120" t="s">
-        <v>407</v>
-      </c>
-      <c r="C120">
-        <v>47.503332863504447</v>
-      </c>
-      <c r="D120">
-        <v>7.5770135285257956</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121" t="s">
-        <v>408</v>
-      </c>
-      <c r="C121">
-        <v>47.192525806627415</v>
-      </c>
-      <c r="D121">
-        <v>8.5025953004376724</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
-      <c r="B122" t="s">
-        <v>409</v>
-      </c>
-      <c r="C122">
-        <v>46.197778440184173</v>
-      </c>
-      <c r="D122">
-        <v>8.7492453882474219</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
-      <c r="B123" t="s">
-        <v>410</v>
-      </c>
-      <c r="C123">
-        <v>46.333583205772456</v>
-      </c>
-      <c r="D123">
-        <v>8.9793979537338995</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4">
-      <c r="B124" t="s">
-        <v>411</v>
-      </c>
-      <c r="C124">
-        <v>46.340257020596965</v>
-      </c>
-      <c r="D124">
-        <v>9.2127758729274198</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
-      <c r="B125" t="s">
-        <v>412</v>
-      </c>
-      <c r="C125">
-        <v>47.497542653552287</v>
-      </c>
-      <c r="D125">
-        <v>8.9315918186612357</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="B126" t="s">
-        <v>413</v>
-      </c>
-      <c r="C126">
-        <v>46.162021135169752</v>
-      </c>
-      <c r="D126">
-        <v>8.9122525816708951</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="B127" t="s">
-        <v>414</v>
-      </c>
-      <c r="C127">
-        <v>46.411435336637261</v>
-      </c>
-      <c r="D127">
-        <v>8.6126265598333376</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128" t="s">
-        <v>415</v>
-      </c>
-      <c r="C128">
-        <v>47.472181885969455</v>
-      </c>
-      <c r="D128">
-        <v>7.862020493690677</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129" t="s">
-        <v>416</v>
-      </c>
-      <c r="C129">
-        <v>47.452839734944206</v>
-      </c>
-      <c r="D129">
-        <v>8.4518037652382549</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130" t="s">
-        <v>417</v>
-      </c>
-      <c r="C130">
-        <v>47.378105927066514</v>
-      </c>
-      <c r="D130">
-        <v>8.2848809002281207</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" t="s">
-        <v>418</v>
-      </c>
-      <c r="C131">
-        <v>47.115092797975542</v>
-      </c>
-      <c r="D131">
-        <v>8.3367437842075223</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4">
-      <c r="B132" t="s">
-        <v>419</v>
-      </c>
-      <c r="C132">
-        <v>46.028484492512405</v>
-      </c>
-      <c r="D132">
-        <v>8.9205901102955742</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4">
-      <c r="B133" t="s">
-        <v>420</v>
-      </c>
-      <c r="C133">
-        <v>47.365499855192191</v>
-      </c>
-      <c r="D133">
-        <v>7.9731469676031752</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" t="s">
-        <v>421</v>
-      </c>
-      <c r="C134">
-        <v>47.598960217274261</v>
-      </c>
-      <c r="D134">
-        <v>8.1833885380782423</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4">
-      <c r="B135" t="s">
-        <v>422</v>
-      </c>
-      <c r="C135">
-        <v>46.765219065594323</v>
-      </c>
-      <c r="D135">
-        <v>9.4186944777386383</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4">
-      <c r="B136" t="s">
-        <v>423</v>
-      </c>
-      <c r="C136">
-        <v>46.395764934452949</v>
-      </c>
-      <c r="D136">
-        <v>8.1308582732979851</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" t="s">
-        <v>424</v>
-      </c>
-      <c r="C137">
-        <v>46.774712160461192</v>
-      </c>
-      <c r="D137">
-        <v>9.1952002264269037</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4">
-      <c r="B138" t="s">
-        <v>425</v>
-      </c>
-      <c r="C138">
-        <v>46.167302808465202</v>
-      </c>
-      <c r="D138">
-        <v>8.1183564066559004</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4">
-      <c r="B139" t="s">
-        <v>426</v>
-      </c>
-      <c r="C139">
-        <v>46.188234494031683</v>
-      </c>
-      <c r="D139">
-        <v>8.0701490996033112</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" t="s">
-        <v>427</v>
-      </c>
-      <c r="C140">
-        <v>47.539015634556947</v>
-      </c>
-      <c r="D140">
-        <v>7.7524068439336924</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4">
-      <c r="B141" t="s">
-        <v>428</v>
-      </c>
-      <c r="C141">
-        <v>47.154942264585237</v>
-      </c>
-      <c r="D141">
-        <v>7.7918813512983336</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4">
-      <c r="B142" t="s">
-        <v>429</v>
-      </c>
-      <c r="C142">
-        <v>46.491577066054226</v>
-      </c>
-      <c r="D142">
-        <v>7.2732837108404942</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" t="s">
-        <v>430</v>
-      </c>
-      <c r="C143">
-        <v>46.526902581268999</v>
-      </c>
-      <c r="D143">
-        <v>8.5970130861268519</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4">
-      <c r="B144" t="s">
-        <v>431</v>
-      </c>
-      <c r="C144">
-        <v>46.546200095956507</v>
-      </c>
-      <c r="D144">
-        <v>6.5707150506742265</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" t="s">
-        <v>432</v>
-      </c>
-      <c r="C145">
-        <v>47.302672807623779</v>
-      </c>
-      <c r="D145">
-        <v>9.5558757704346071</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" t="s">
-        <v>433</v>
-      </c>
-      <c r="C146">
-        <v>47.549929778349131</v>
-      </c>
-      <c r="D146">
-        <v>8.0505862642923702</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" t="s">
-        <v>434</v>
-      </c>
-      <c r="C147">
-        <v>47.534182026511104</v>
-      </c>
-      <c r="D147">
-        <v>8.6975363672935035</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" t="s">
-        <v>435</v>
-      </c>
-      <c r="C148">
-        <v>47.186874616216762</v>
-      </c>
-      <c r="D148">
-        <v>8.6845093233496922</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" t="s">
-        <v>436</v>
-      </c>
-      <c r="C149">
-        <v>46.541607589484336</v>
-      </c>
-      <c r="D149">
-        <v>6.4691836479843738</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" t="s">
-        <v>437</v>
-      </c>
-      <c r="C150">
-        <v>46.266170983209811</v>
-      </c>
-      <c r="D150">
-        <v>6.9744475162681168</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" t="s">
-        <v>438</v>
-      </c>
-      <c r="C151">
-        <v>46.811139511097466</v>
-      </c>
-      <c r="D151">
-        <v>9.378873087203484</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" t="s">
-        <v>439</v>
-      </c>
-      <c r="C152">
-        <v>46.680751374315896</v>
-      </c>
-      <c r="D152">
-        <v>7.6548635065014201</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" t="s">
-        <v>440</v>
-      </c>
-      <c r="C153">
-        <v>46.0317529216154</v>
-      </c>
-      <c r="D153">
-        <v>7.3084509725129267</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" t="s">
-        <v>441</v>
-      </c>
-      <c r="C154">
-        <v>46.15852172448291</v>
-      </c>
-      <c r="D154">
-        <v>7.2094009496203837</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" t="s">
-        <v>442</v>
-      </c>
-      <c r="C155">
-        <v>47.339117940297619</v>
-      </c>
-      <c r="D155">
-        <v>9.5780970318362559</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" t="s">
-        <v>443</v>
-      </c>
-      <c r="C156">
-        <v>47.657573790258297</v>
-      </c>
-      <c r="D156">
-        <v>8.7754632624143429</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" t="s">
-        <v>444</v>
-      </c>
-      <c r="C157">
-        <v>47.585912287118212</v>
-      </c>
-      <c r="D157">
-        <v>7.8435782904311289</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" t="s">
-        <v>445</v>
-      </c>
-      <c r="C158">
-        <v>47.406318762945403</v>
-      </c>
-      <c r="D158">
-        <v>8.105761472055045</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" t="s">
-        <v>446</v>
-      </c>
-      <c r="C159">
-        <v>47.427363293638969</v>
-      </c>
-      <c r="D159">
-        <v>8.3803937353034943</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" t="s">
-        <v>447</v>
-      </c>
-      <c r="C160">
-        <v>47.397732455842615</v>
-      </c>
-      <c r="D160">
-        <v>9.3025128506927892</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" t="s">
-        <v>448</v>
-      </c>
-      <c r="C161">
-        <v>47.481915935925542</v>
-      </c>
-      <c r="D161">
-        <v>9.4326555268370722</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" t="s">
-        <v>449</v>
-      </c>
-      <c r="C162">
-        <v>46.110634293306326</v>
-      </c>
-      <c r="D162">
-        <v>7.0612643589312309</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" t="s">
-        <v>450</v>
-      </c>
-      <c r="C163">
-        <v>46.44140479554256</v>
-      </c>
-      <c r="D163">
-        <v>8.8374874894540767</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" t="s">
-        <v>451</v>
-      </c>
-      <c r="C164">
-        <v>46.350910363932599</v>
-      </c>
-      <c r="D164">
-        <v>8.0409180183520075</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" t="s">
-        <v>452</v>
-      </c>
-      <c r="C165">
-        <v>47.058633982952401</v>
-      </c>
-      <c r="D165">
-        <v>8.2563745533433206</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" t="s">
-        <v>453</v>
-      </c>
-      <c r="C166">
-        <v>47.555988773696292</v>
-      </c>
-      <c r="D166">
-        <v>8.2320077689227631</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" t="s">
-        <v>454</v>
-      </c>
-      <c r="C167">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D167">
-        <v>6.289697641356212</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4">
-      <c r="B168" t="s">
-        <v>455</v>
-      </c>
-      <c r="C168">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D168">
-        <v>6.289697641356212</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" t="s">
-        <v>456</v>
-      </c>
-      <c r="C169">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D169">
-        <v>6.289697641356212</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" t="s">
-        <v>457</v>
-      </c>
-      <c r="C170">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D170">
-        <v>6.9349650942374748</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" t="s">
-        <v>458</v>
-      </c>
-      <c r="C171">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D171">
-        <v>6.9349650942374748</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" t="s">
-        <v>459</v>
-      </c>
-      <c r="C172">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D172">
-        <v>6.9349650942374748</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" t="s">
-        <v>460</v>
-      </c>
-      <c r="C173">
-        <v>47.486990272793413</v>
-      </c>
-      <c r="D173">
-        <v>6.9349650942374748</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" t="s">
-        <v>461</v>
-      </c>
-      <c r="C174">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D174">
-        <v>7.5802325471187393</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" t="s">
-        <v>462</v>
-      </c>
-      <c r="C175">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D175">
-        <v>7.5802325471187393</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4">
-      <c r="B176" t="s">
-        <v>463</v>
-      </c>
-      <c r="C176">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D176">
-        <v>7.5802325471187393</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4">
-      <c r="B177" t="s">
-        <v>464</v>
-      </c>
-      <c r="C177">
-        <v>47.486990272793413</v>
-      </c>
-      <c r="D177">
-        <v>7.5802325471187393</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4">
-      <c r="B178" t="s">
-        <v>465</v>
-      </c>
-      <c r="C178">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D178">
-        <v>8.225500000000002</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4">
-      <c r="B179" t="s">
-        <v>466</v>
-      </c>
-      <c r="C179">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D179">
-        <v>8.225500000000002</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4">
-      <c r="B180" t="s">
-        <v>467</v>
-      </c>
-      <c r="C180">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D180">
-        <v>8.225500000000002</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" t="s">
-        <v>468</v>
-      </c>
-      <c r="C181">
-        <v>47.486990272793413</v>
-      </c>
-      <c r="D181">
-        <v>8.225500000000002</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4">
-      <c r="B182" t="s">
-        <v>469</v>
-      </c>
-      <c r="C182">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D182">
-        <v>8.8707674528812674</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4">
-      <c r="B183" t="s">
-        <v>470</v>
-      </c>
-      <c r="C183">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D183">
-        <v>8.8707674528812674</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4">
-      <c r="B184" t="s">
-        <v>471</v>
-      </c>
-      <c r="C184">
-        <v>47.486990272793413</v>
-      </c>
-      <c r="D184">
-        <v>8.8707674528812674</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4">
-      <c r="B185" t="s">
-        <v>472</v>
-      </c>
-      <c r="C185">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D185">
-        <v>9.5160349057625293</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4">
-      <c r="B186" t="s">
-        <v>473</v>
-      </c>
-      <c r="C186">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D186">
-        <v>9.5160349057625293</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4">
-      <c r="B187" t="s">
-        <v>474</v>
-      </c>
-      <c r="C187">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D187">
-        <v>9.5160349057625293</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4">
-      <c r="B188" t="s">
-        <v>475</v>
-      </c>
-      <c r="C188">
-        <v>47.486990272793413</v>
-      </c>
-      <c r="D188">
-        <v>9.5160349057625293</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4">
-      <c r="B189" t="s">
-        <v>476</v>
-      </c>
-      <c r="C189">
-        <v>46.138009727206594</v>
-      </c>
-      <c r="D189">
-        <v>10.161302358643791</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4">
-      <c r="B190" t="s">
-        <v>477</v>
-      </c>
-      <c r="C190">
-        <v>46.587669909068872</v>
-      </c>
-      <c r="D190">
-        <v>10.161302358643791</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4">
-      <c r="B191" t="s">
-        <v>478</v>
-      </c>
-      <c r="C191">
-        <v>47.037330090931135</v>
-      </c>
-      <c r="D191">
-        <v>10.161302358643791</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC06C61E-6B66-4FC8-9526-1932D145970C}">
-  <dimension ref="B2:D184"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" t="s">
-        <v>297</v>
-      </c>
-      <c r="C8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D8" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9" t="s">
-        <v>303</v>
-      </c>
-      <c r="D9" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>297</v>
-      </c>
-      <c r="C10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D10" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" t="s">
-        <v>297</v>
-      </c>
-      <c r="C12" t="s">
-        <v>306</v>
-      </c>
-      <c r="D12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
-        <v>297</v>
-      </c>
-      <c r="C14" t="s">
-        <v>308</v>
-      </c>
-      <c r="D14" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D15" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" t="s">
-        <v>297</v>
-      </c>
-      <c r="C16" t="s">
-        <v>310</v>
-      </c>
-      <c r="D16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>297</v>
-      </c>
-      <c r="C17" t="s">
-        <v>311</v>
-      </c>
-      <c r="D17" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C18" t="s">
-        <v>312</v>
-      </c>
-      <c r="D18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" t="s">
-        <v>297</v>
-      </c>
-      <c r="C19" t="s">
-        <v>313</v>
-      </c>
-      <c r="D19" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" t="s">
-        <v>314</v>
-      </c>
-      <c r="D20" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" t="s">
-        <v>297</v>
-      </c>
-      <c r="C21" t="s">
-        <v>315</v>
-      </c>
-      <c r="D21" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" t="s">
-        <v>316</v>
-      </c>
-      <c r="D22" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" t="s">
-        <v>297</v>
-      </c>
-      <c r="C23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D23" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" t="s">
-        <v>318</v>
-      </c>
-      <c r="D24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" t="s">
-        <v>297</v>
-      </c>
-      <c r="C25" t="s">
-        <v>319</v>
-      </c>
-      <c r="D25" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" t="s">
-        <v>297</v>
-      </c>
-      <c r="C26" t="s">
-        <v>320</v>
-      </c>
-      <c r="D26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C27" t="s">
-        <v>321</v>
-      </c>
-      <c r="D27" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" t="s">
-        <v>297</v>
-      </c>
-      <c r="C28" t="s">
-        <v>322</v>
-      </c>
-      <c r="D28" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" t="s">
-        <v>297</v>
-      </c>
-      <c r="C29" t="s">
-        <v>323</v>
-      </c>
-      <c r="D29" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" t="s">
-        <v>297</v>
-      </c>
-      <c r="C30" t="s">
-        <v>324</v>
-      </c>
-      <c r="D30" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" t="s">
-        <v>297</v>
-      </c>
-      <c r="C31" t="s">
-        <v>325</v>
-      </c>
-      <c r="D31" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" t="s">
-        <v>297</v>
-      </c>
-      <c r="C32" t="s">
-        <v>326</v>
-      </c>
-      <c r="D32" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
-        <v>297</v>
-      </c>
-      <c r="C33" t="s">
-        <v>327</v>
-      </c>
-      <c r="D33" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C34" t="s">
-        <v>328</v>
-      </c>
-      <c r="D34" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
-        <v>297</v>
-      </c>
-      <c r="C35" t="s">
-        <v>329</v>
-      </c>
-      <c r="D35" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
-        <v>297</v>
-      </c>
-      <c r="C36" t="s">
-        <v>330</v>
-      </c>
-      <c r="D36" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
-        <v>297</v>
-      </c>
-      <c r="C37" t="s">
-        <v>331</v>
-      </c>
-      <c r="D37" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
-        <v>297</v>
-      </c>
-      <c r="C38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D38" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>297</v>
-      </c>
-      <c r="C39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D39" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
-        <v>297</v>
-      </c>
-      <c r="C40" t="s">
-        <v>334</v>
-      </c>
-      <c r="D40" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
-        <v>297</v>
-      </c>
-      <c r="C41" t="s">
-        <v>335</v>
-      </c>
-      <c r="D41" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>297</v>
-      </c>
-      <c r="C42" t="s">
-        <v>336</v>
-      </c>
-      <c r="D42" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
-        <v>297</v>
-      </c>
-      <c r="C43" t="s">
-        <v>337</v>
-      </c>
-      <c r="D43" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
-        <v>297</v>
-      </c>
-      <c r="C44" t="s">
-        <v>338</v>
-      </c>
-      <c r="D44" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
-        <v>297</v>
-      </c>
-      <c r="C45" t="s">
-        <v>339</v>
-      </c>
-      <c r="D45" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
-        <v>297</v>
-      </c>
-      <c r="C46" t="s">
-        <v>340</v>
-      </c>
-      <c r="D46" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
-        <v>297</v>
-      </c>
-      <c r="C47" t="s">
-        <v>341</v>
-      </c>
-      <c r="D47" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
-        <v>297</v>
-      </c>
-      <c r="C48" t="s">
-        <v>342</v>
-      </c>
-      <c r="D48" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" t="s">
-        <v>297</v>
-      </c>
-      <c r="C49" t="s">
-        <v>343</v>
-      </c>
-      <c r="D49" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" t="s">
-        <v>297</v>
-      </c>
-      <c r="C50" t="s">
-        <v>344</v>
-      </c>
-      <c r="D50" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" t="s">
-        <v>297</v>
-      </c>
-      <c r="C51" t="s">
-        <v>345</v>
-      </c>
-      <c r="D51" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" t="s">
-        <v>297</v>
-      </c>
-      <c r="C52" t="s">
-        <v>346</v>
-      </c>
-      <c r="D52" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" t="s">
-        <v>297</v>
-      </c>
-      <c r="C53" t="s">
-        <v>347</v>
-      </c>
-      <c r="D53" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" t="s">
-        <v>297</v>
-      </c>
-      <c r="C54" t="s">
-        <v>348</v>
-      </c>
-      <c r="D54" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" t="s">
-        <v>297</v>
-      </c>
-      <c r="C55" t="s">
-        <v>349</v>
-      </c>
-      <c r="D55" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" t="s">
-        <v>297</v>
-      </c>
-      <c r="C56" t="s">
-        <v>350</v>
-      </c>
-      <c r="D56" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" t="s">
-        <v>297</v>
-      </c>
-      <c r="C57" t="s">
-        <v>351</v>
-      </c>
-      <c r="D57" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" t="s">
-        <v>297</v>
-      </c>
-      <c r="C58" t="s">
-        <v>352</v>
-      </c>
-      <c r="D58" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" t="s">
-        <v>297</v>
-      </c>
-      <c r="C59" t="s">
-        <v>353</v>
-      </c>
-      <c r="D59" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" t="s">
-        <v>297</v>
-      </c>
-      <c r="C60" t="s">
-        <v>354</v>
-      </c>
-      <c r="D60" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" t="s">
-        <v>297</v>
-      </c>
-      <c r="C61" t="s">
-        <v>355</v>
-      </c>
-      <c r="D61" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62" t="s">
-        <v>297</v>
-      </c>
-      <c r="C62" t="s">
-        <v>356</v>
-      </c>
-      <c r="D62" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63" t="s">
-        <v>297</v>
-      </c>
-      <c r="C63" t="s">
-        <v>357</v>
-      </c>
-      <c r="D63" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" t="s">
-        <v>297</v>
-      </c>
-      <c r="C64" t="s">
-        <v>358</v>
-      </c>
-      <c r="D64" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" t="s">
-        <v>297</v>
-      </c>
-      <c r="C65" t="s">
-        <v>359</v>
-      </c>
-      <c r="D65" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" t="s">
-        <v>297</v>
-      </c>
-      <c r="C66" t="s">
-        <v>360</v>
-      </c>
-      <c r="D66" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" t="s">
-        <v>297</v>
-      </c>
-      <c r="C67" t="s">
-        <v>361</v>
-      </c>
-      <c r="D67" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" t="s">
-        <v>297</v>
-      </c>
-      <c r="C68" t="s">
-        <v>362</v>
-      </c>
-      <c r="D68" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" t="s">
-        <v>297</v>
-      </c>
-      <c r="C69" t="s">
-        <v>363</v>
-      </c>
-      <c r="D69" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" t="s">
-        <v>297</v>
-      </c>
-      <c r="C70" t="s">
-        <v>364</v>
-      </c>
-      <c r="D70" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" t="s">
-        <v>297</v>
-      </c>
-      <c r="C71" t="s">
-        <v>365</v>
-      </c>
-      <c r="D71" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" t="s">
-        <v>366</v>
-      </c>
-      <c r="D72" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" t="s">
-        <v>297</v>
-      </c>
-      <c r="C73" t="s">
-        <v>367</v>
-      </c>
-      <c r="D73" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" t="s">
-        <v>297</v>
-      </c>
-      <c r="C74" t="s">
-        <v>368</v>
-      </c>
-      <c r="D74" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" t="s">
-        <v>297</v>
-      </c>
-      <c r="C75" t="s">
-        <v>369</v>
-      </c>
-      <c r="D75" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" t="s">
-        <v>297</v>
-      </c>
-      <c r="C76" t="s">
-        <v>370</v>
-      </c>
-      <c r="D76" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77" t="s">
-        <v>297</v>
-      </c>
-      <c r="C77" t="s">
-        <v>371</v>
-      </c>
-      <c r="D77" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="B78" t="s">
-        <v>297</v>
-      </c>
-      <c r="C78" t="s">
-        <v>372</v>
-      </c>
-      <c r="D78" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4">
-      <c r="B79" t="s">
-        <v>297</v>
-      </c>
-      <c r="C79" t="s">
-        <v>373</v>
-      </c>
-      <c r="D79" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80" t="s">
-        <v>297</v>
-      </c>
-      <c r="C80" t="s">
-        <v>374</v>
-      </c>
-      <c r="D80" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" t="s">
-        <v>297</v>
-      </c>
-      <c r="C81" t="s">
-        <v>375</v>
-      </c>
-      <c r="D81" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82" t="s">
-        <v>297</v>
-      </c>
-      <c r="C82" t="s">
-        <v>376</v>
-      </c>
-      <c r="D82" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="B83" t="s">
-        <v>297</v>
-      </c>
-      <c r="C83" t="s">
-        <v>377</v>
-      </c>
-      <c r="D83" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="B84" t="s">
-        <v>297</v>
-      </c>
-      <c r="C84" t="s">
-        <v>378</v>
-      </c>
-      <c r="D84" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85" t="s">
-        <v>297</v>
-      </c>
-      <c r="C85" t="s">
-        <v>379</v>
-      </c>
-      <c r="D85" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86" t="s">
-        <v>297</v>
-      </c>
-      <c r="C86" t="s">
-        <v>380</v>
-      </c>
-      <c r="D86" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87" t="s">
-        <v>297</v>
-      </c>
-      <c r="C87" t="s">
-        <v>381</v>
-      </c>
-      <c r="D87" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" t="s">
-        <v>297</v>
-      </c>
-      <c r="C88" t="s">
-        <v>382</v>
-      </c>
-      <c r="D88" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" t="s">
-        <v>297</v>
-      </c>
-      <c r="C89" t="s">
-        <v>383</v>
-      </c>
-      <c r="D89" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" t="s">
-        <v>297</v>
-      </c>
-      <c r="C90" t="s">
-        <v>384</v>
-      </c>
-      <c r="D90" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91" t="s">
-        <v>297</v>
-      </c>
-      <c r="C91" t="s">
-        <v>385</v>
-      </c>
-      <c r="D91" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92" t="s">
-        <v>297</v>
-      </c>
-      <c r="C92" t="s">
-        <v>386</v>
-      </c>
-      <c r="D92" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93" t="s">
-        <v>297</v>
-      </c>
-      <c r="C93" t="s">
-        <v>387</v>
-      </c>
-      <c r="D93" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94" t="s">
-        <v>297</v>
-      </c>
-      <c r="C94" t="s">
-        <v>388</v>
-      </c>
-      <c r="D94" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95" t="s">
-        <v>297</v>
-      </c>
-      <c r="C95" t="s">
-        <v>389</v>
-      </c>
-      <c r="D95" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="B96" t="s">
-        <v>297</v>
-      </c>
-      <c r="C96" t="s">
-        <v>390</v>
-      </c>
-      <c r="D96" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97" t="s">
-        <v>297</v>
-      </c>
-      <c r="C97" t="s">
-        <v>391</v>
-      </c>
-      <c r="D97" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98" t="s">
-        <v>297</v>
-      </c>
-      <c r="C98" t="s">
-        <v>392</v>
-      </c>
-      <c r="D98" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99" t="s">
-        <v>297</v>
-      </c>
-      <c r="C99" t="s">
-        <v>393</v>
-      </c>
-      <c r="D99" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100" t="s">
-        <v>297</v>
-      </c>
-      <c r="C100" t="s">
-        <v>394</v>
-      </c>
-      <c r="D100" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101" t="s">
-        <v>297</v>
-      </c>
-      <c r="C101" t="s">
-        <v>395</v>
-      </c>
-      <c r="D101" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102" t="s">
-        <v>297</v>
-      </c>
-      <c r="C102" t="s">
-        <v>396</v>
-      </c>
-      <c r="D102" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103" t="s">
-        <v>297</v>
-      </c>
-      <c r="C103" t="s">
-        <v>397</v>
-      </c>
-      <c r="D103" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104" t="s">
-        <v>297</v>
-      </c>
-      <c r="C104" t="s">
-        <v>398</v>
-      </c>
-      <c r="D104" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" t="s">
-        <v>297</v>
-      </c>
-      <c r="C105" t="s">
-        <v>399</v>
-      </c>
-      <c r="D105" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" t="s">
-        <v>297</v>
-      </c>
-      <c r="C106" t="s">
-        <v>400</v>
-      </c>
-      <c r="D106" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107" t="s">
-        <v>297</v>
-      </c>
-      <c r="C107" t="s">
-        <v>401</v>
-      </c>
-      <c r="D107" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" t="s">
-        <v>297</v>
-      </c>
-      <c r="C108" t="s">
-        <v>402</v>
-      </c>
-      <c r="D108" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" t="s">
-        <v>297</v>
-      </c>
-      <c r="C109" t="s">
-        <v>403</v>
-      </c>
-      <c r="D109" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" t="s">
-        <v>297</v>
-      </c>
-      <c r="C110" t="s">
-        <v>404</v>
-      </c>
-      <c r="D110" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" t="s">
-        <v>297</v>
-      </c>
-      <c r="C111" t="s">
-        <v>405</v>
-      </c>
-      <c r="D111" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" t="s">
-        <v>297</v>
-      </c>
-      <c r="C112" t="s">
-        <v>406</v>
-      </c>
-      <c r="D112" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
-      <c r="B113" t="s">
-        <v>297</v>
-      </c>
-      <c r="C113" t="s">
-        <v>407</v>
-      </c>
-      <c r="D113" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114" t="s">
-        <v>297</v>
-      </c>
-      <c r="C114" t="s">
-        <v>408</v>
-      </c>
-      <c r="D114" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115" t="s">
-        <v>297</v>
-      </c>
-      <c r="C115" t="s">
-        <v>409</v>
-      </c>
-      <c r="D115" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116" t="s">
-        <v>297</v>
-      </c>
-      <c r="C116" t="s">
-        <v>410</v>
-      </c>
-      <c r="D116" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
-      <c r="B117" t="s">
-        <v>297</v>
-      </c>
-      <c r="C117" t="s">
-        <v>411</v>
-      </c>
-      <c r="D117" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118" t="s">
-        <v>297</v>
-      </c>
-      <c r="C118" t="s">
-        <v>412</v>
-      </c>
-      <c r="D118" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" t="s">
-        <v>297</v>
-      </c>
-      <c r="C119" t="s">
-        <v>413</v>
-      </c>
-      <c r="D119" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
-      <c r="B120" t="s">
-        <v>297</v>
-      </c>
-      <c r="C120" t="s">
-        <v>414</v>
-      </c>
-      <c r="D120" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121" t="s">
-        <v>297</v>
-      </c>
-      <c r="C121" t="s">
-        <v>415</v>
-      </c>
-      <c r="D121" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
-      <c r="B122" t="s">
-        <v>297</v>
-      </c>
-      <c r="C122" t="s">
-        <v>416</v>
-      </c>
-      <c r="D122" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
-      <c r="B123" t="s">
-        <v>297</v>
-      </c>
-      <c r="C123" t="s">
-        <v>417</v>
-      </c>
-      <c r="D123" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4">
-      <c r="B124" t="s">
-        <v>297</v>
-      </c>
-      <c r="C124" t="s">
-        <v>418</v>
-      </c>
-      <c r="D124" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
-      <c r="B125" t="s">
-        <v>297</v>
-      </c>
-      <c r="C125" t="s">
-        <v>419</v>
-      </c>
-      <c r="D125" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="B126" t="s">
-        <v>297</v>
-      </c>
-      <c r="C126" t="s">
-        <v>420</v>
-      </c>
-      <c r="D126" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="B127" t="s">
-        <v>297</v>
-      </c>
-      <c r="C127" t="s">
-        <v>421</v>
-      </c>
-      <c r="D127" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128" t="s">
-        <v>297</v>
-      </c>
-      <c r="C128" t="s">
-        <v>422</v>
-      </c>
-      <c r="D128" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129" t="s">
-        <v>297</v>
-      </c>
-      <c r="C129" t="s">
-        <v>423</v>
-      </c>
-      <c r="D129" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130" t="s">
-        <v>297</v>
-      </c>
-      <c r="C130" t="s">
-        <v>424</v>
-      </c>
-      <c r="D130" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" t="s">
-        <v>297</v>
-      </c>
-      <c r="C131" t="s">
-        <v>425</v>
-      </c>
-      <c r="D131" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4">
-      <c r="B132" t="s">
-        <v>297</v>
-      </c>
-      <c r="C132" t="s">
-        <v>426</v>
-      </c>
-      <c r="D132" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4">
-      <c r="B133" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" t="s">
-        <v>427</v>
-      </c>
-      <c r="D133" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" t="s">
-        <v>297</v>
-      </c>
-      <c r="C134" t="s">
-        <v>428</v>
-      </c>
-      <c r="D134" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4">
-      <c r="B135" t="s">
-        <v>297</v>
-      </c>
-      <c r="C135" t="s">
-        <v>429</v>
-      </c>
-      <c r="D135" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4">
-      <c r="B136" t="s">
-        <v>297</v>
-      </c>
-      <c r="C136" t="s">
-        <v>430</v>
-      </c>
-      <c r="D136" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" t="s">
-        <v>297</v>
-      </c>
-      <c r="C137" t="s">
-        <v>431</v>
-      </c>
-      <c r="D137" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4">
-      <c r="B138" t="s">
-        <v>297</v>
-      </c>
-      <c r="C138" t="s">
-        <v>432</v>
-      </c>
-      <c r="D138" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4">
-      <c r="B139" t="s">
-        <v>297</v>
-      </c>
-      <c r="C139" t="s">
-        <v>433</v>
-      </c>
-      <c r="D139" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" t="s">
-        <v>297</v>
-      </c>
-      <c r="C140" t="s">
-        <v>434</v>
-      </c>
-      <c r="D140" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4">
-      <c r="B141" t="s">
-        <v>297</v>
-      </c>
-      <c r="C141" t="s">
-        <v>435</v>
-      </c>
-      <c r="D141" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4">
-      <c r="B142" t="s">
-        <v>297</v>
-      </c>
-      <c r="C142" t="s">
-        <v>436</v>
-      </c>
-      <c r="D142" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" t="s">
-        <v>297</v>
-      </c>
-      <c r="C143" t="s">
-        <v>437</v>
-      </c>
-      <c r="D143" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4">
-      <c r="B144" t="s">
-        <v>297</v>
-      </c>
-      <c r="C144" t="s">
-        <v>438</v>
-      </c>
-      <c r="D144" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" t="s">
-        <v>297</v>
-      </c>
-      <c r="C145" t="s">
-        <v>439</v>
-      </c>
-      <c r="D145" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" t="s">
-        <v>297</v>
-      </c>
-      <c r="C146" t="s">
-        <v>440</v>
-      </c>
-      <c r="D146" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" t="s">
-        <v>297</v>
-      </c>
-      <c r="C147" t="s">
-        <v>441</v>
-      </c>
-      <c r="D147" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" t="s">
-        <v>297</v>
-      </c>
-      <c r="C148" t="s">
-        <v>442</v>
-      </c>
-      <c r="D148" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" t="s">
-        <v>297</v>
-      </c>
-      <c r="C149" t="s">
-        <v>443</v>
-      </c>
-      <c r="D149" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" t="s">
-        <v>297</v>
-      </c>
-      <c r="C150" t="s">
-        <v>444</v>
-      </c>
-      <c r="D150" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" t="s">
-        <v>297</v>
-      </c>
-      <c r="C151" t="s">
-        <v>445</v>
-      </c>
-      <c r="D151" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" t="s">
-        <v>297</v>
-      </c>
-      <c r="C152" t="s">
-        <v>446</v>
-      </c>
-      <c r="D152" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" t="s">
-        <v>297</v>
-      </c>
-      <c r="C153" t="s">
-        <v>447</v>
-      </c>
-      <c r="D153" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" t="s">
-        <v>297</v>
-      </c>
-      <c r="C154" t="s">
-        <v>448</v>
-      </c>
-      <c r="D154" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" t="s">
-        <v>297</v>
-      </c>
-      <c r="C155" t="s">
-        <v>449</v>
-      </c>
-      <c r="D155" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" t="s">
-        <v>297</v>
-      </c>
-      <c r="C156" t="s">
-        <v>450</v>
-      </c>
-      <c r="D156" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" t="s">
-        <v>297</v>
-      </c>
-      <c r="C157" t="s">
-        <v>451</v>
-      </c>
-      <c r="D157" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" t="s">
-        <v>297</v>
-      </c>
-      <c r="C158" t="s">
-        <v>452</v>
-      </c>
-      <c r="D158" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" t="s">
-        <v>297</v>
-      </c>
-      <c r="C159" t="s">
-        <v>453</v>
-      </c>
-      <c r="D159" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" t="s">
-        <v>297</v>
-      </c>
-      <c r="C160" t="s">
-        <v>454</v>
-      </c>
-      <c r="D160" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" t="s">
-        <v>455</v>
-      </c>
-      <c r="D161" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" t="s">
-        <v>297</v>
-      </c>
-      <c r="C162" t="s">
-        <v>456</v>
-      </c>
-      <c r="D162" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" t="s">
-        <v>297</v>
-      </c>
-      <c r="C163" t="s">
-        <v>457</v>
-      </c>
-      <c r="D163" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" t="s">
-        <v>297</v>
-      </c>
-      <c r="C164" t="s">
-        <v>458</v>
-      </c>
-      <c r="D164" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" t="s">
-        <v>297</v>
-      </c>
-      <c r="C165" t="s">
-        <v>459</v>
-      </c>
-      <c r="D165" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" t="s">
-        <v>297</v>
-      </c>
-      <c r="C166" t="s">
-        <v>460</v>
-      </c>
-      <c r="D166" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" t="s">
-        <v>297</v>
-      </c>
-      <c r="C167" t="s">
-        <v>461</v>
-      </c>
-      <c r="D167" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4">
-      <c r="B168" t="s">
-        <v>297</v>
-      </c>
-      <c r="C168" t="s">
-        <v>462</v>
-      </c>
-      <c r="D168" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" t="s">
-        <v>297</v>
-      </c>
-      <c r="C169" t="s">
-        <v>463</v>
-      </c>
-      <c r="D169" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" t="s">
-        <v>297</v>
-      </c>
-      <c r="C170" t="s">
-        <v>464</v>
-      </c>
-      <c r="D170" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" t="s">
-        <v>297</v>
-      </c>
-      <c r="C171" t="s">
-        <v>465</v>
-      </c>
-      <c r="D171" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" t="s">
-        <v>297</v>
-      </c>
-      <c r="C172" t="s">
-        <v>466</v>
-      </c>
-      <c r="D172" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" t="s">
-        <v>297</v>
-      </c>
-      <c r="C173" t="s">
-        <v>467</v>
-      </c>
-      <c r="D173" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" t="s">
-        <v>297</v>
-      </c>
-      <c r="C174" t="s">
-        <v>468</v>
-      </c>
-      <c r="D174" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" t="s">
-        <v>297</v>
-      </c>
-      <c r="C175" t="s">
-        <v>469</v>
-      </c>
-      <c r="D175" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4">
-      <c r="B176" t="s">
-        <v>297</v>
-      </c>
-      <c r="C176" t="s">
-        <v>470</v>
-      </c>
-      <c r="D176" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4">
-      <c r="B177" t="s">
-        <v>297</v>
-      </c>
-      <c r="C177" t="s">
-        <v>471</v>
-      </c>
-      <c r="D177" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4">
-      <c r="B178" t="s">
-        <v>297</v>
-      </c>
-      <c r="C178" t="s">
-        <v>472</v>
-      </c>
-      <c r="D178" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4">
-      <c r="B179" t="s">
-        <v>297</v>
-      </c>
-      <c r="C179" t="s">
-        <v>473</v>
-      </c>
-      <c r="D179" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4">
-      <c r="B180" t="s">
-        <v>297</v>
-      </c>
-      <c r="C180" t="s">
-        <v>474</v>
-      </c>
-      <c r="D180" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" t="s">
-        <v>297</v>
-      </c>
-      <c r="C181" t="s">
-        <v>475</v>
-      </c>
-      <c r="D181" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4">
-      <c r="B182" t="s">
-        <v>297</v>
-      </c>
-      <c r="C182" t="s">
-        <v>476</v>
-      </c>
-      <c r="D182" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4">
-      <c r="B183" t="s">
-        <v>297</v>
-      </c>
-      <c r="C183" t="s">
-        <v>477</v>
-      </c>
-      <c r="D183" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4">
-      <c r="B184" t="s">
-        <v>297</v>
-      </c>
-      <c r="C184" t="s">
-        <v>478</v>
-      </c>
-      <c r="D184" t="s">
-        <v>478</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="B1:X60"/>
@@ -9404,7 +5370,7 @@
         <v>230</v>
       </c>
       <c r="Q6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -9416,7 +5382,7 @@
         <v>244</v>
       </c>
       <c r="W6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="X6" t="s">
         <v>258</v>
@@ -9453,7 +5419,7 @@
         <v>231</v>
       </c>
       <c r="Q7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S7">
         <v>2</v>
@@ -9465,7 +5431,7 @@
         <v>241</v>
       </c>
       <c r="W7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="X7" t="s">
         <v>257</v>
@@ -9502,7 +5468,7 @@
         <v>232</v>
       </c>
       <c r="Q8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S8">
         <v>3</v>
@@ -9514,7 +5480,7 @@
         <v>242</v>
       </c>
       <c r="W8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="X8" t="s">
         <v>256</v>
@@ -9551,7 +5517,7 @@
         <v>233</v>
       </c>
       <c r="Q9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S9">
         <v>4</v>
@@ -9563,7 +5529,7 @@
         <v>240</v>
       </c>
       <c r="W9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="X9" t="s">
         <v>255</v>
@@ -9600,7 +5566,7 @@
         <v>234</v>
       </c>
       <c r="Q10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -9612,7 +5578,7 @@
         <v>247</v>
       </c>
       <c r="W10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="X10" t="s">
         <v>259</v>
@@ -9646,7 +5612,7 @@
         <v>235</v>
       </c>
       <c r="Q11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -9686,7 +5652,7 @@
         <v>236</v>
       </c>
       <c r="Q12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S12">
         <v>7</v>
@@ -9726,7 +5692,7 @@
         <v>237</v>
       </c>
       <c r="Q13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -9766,7 +5732,7 @@
         <v>263</v>
       </c>
       <c r="Q14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -9806,7 +5772,7 @@
         <v>238</v>
       </c>
       <c r="Q15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -9846,7 +5812,7 @@
         <v>239</v>
       </c>
       <c r="Q16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S16">
         <v>11</v>
@@ -9855,7 +5821,7 @@
         <v>263</v>
       </c>
       <c r="U16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="2:17">
@@ -9886,7 +5852,7 @@
         <v>230</v>
       </c>
       <c r="Q17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -9917,7 +5883,7 @@
         <v>231</v>
       </c>
       <c r="Q18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="2:17">
@@ -9948,7 +5914,7 @@
         <v>232</v>
       </c>
       <c r="Q19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="2:17">
@@ -9979,7 +5945,7 @@
         <v>233</v>
       </c>
       <c r="Q20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="2:17">
@@ -10010,7 +5976,7 @@
         <v>234</v>
       </c>
       <c r="Q21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -10041,7 +6007,7 @@
         <v>235</v>
       </c>
       <c r="Q22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -10072,7 +6038,7 @@
         <v>236</v>
       </c>
       <c r="Q23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -10103,7 +6069,7 @@
         <v>237</v>
       </c>
       <c r="Q24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -10134,7 +6100,7 @@
         <v>263</v>
       </c>
       <c r="Q25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -10165,7 +6131,7 @@
         <v>238</v>
       </c>
       <c r="Q26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -10196,7 +6162,7 @@
         <v>239</v>
       </c>
       <c r="Q27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="2:17">
@@ -10227,7 +6193,7 @@
         <v>230</v>
       </c>
       <c r="Q28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -10258,7 +6224,7 @@
         <v>231</v>
       </c>
       <c r="Q29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="2:17">
@@ -10289,7 +6255,7 @@
         <v>232</v>
       </c>
       <c r="Q30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="2:17">
@@ -10320,7 +6286,7 @@
         <v>233</v>
       </c>
       <c r="Q31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -10351,7 +6317,7 @@
         <v>234</v>
       </c>
       <c r="Q32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -10382,7 +6348,7 @@
         <v>235</v>
       </c>
       <c r="Q33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="2:17">
@@ -10413,7 +6379,7 @@
         <v>236</v>
       </c>
       <c r="Q34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -10444,7 +6410,7 @@
         <v>237</v>
       </c>
       <c r="Q35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -10475,7 +6441,7 @@
         <v>263</v>
       </c>
       <c r="Q36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -10506,7 +6472,7 @@
         <v>238</v>
       </c>
       <c r="Q37" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="2:17">
@@ -10537,7 +6503,7 @@
         <v>239</v>
       </c>
       <c r="Q38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -10568,7 +6534,7 @@
         <v>230</v>
       </c>
       <c r="Q39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -10599,7 +6565,7 @@
         <v>231</v>
       </c>
       <c r="Q40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="2:17">
@@ -10630,7 +6596,7 @@
         <v>232</v>
       </c>
       <c r="Q41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="2:17">
@@ -10661,7 +6627,7 @@
         <v>233</v>
       </c>
       <c r="Q42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -10692,7 +6658,7 @@
         <v>234</v>
       </c>
       <c r="Q43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -10723,7 +6689,7 @@
         <v>235</v>
       </c>
       <c r="Q44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -10754,7 +6720,7 @@
         <v>236</v>
       </c>
       <c r="Q45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -10785,7 +6751,7 @@
         <v>237</v>
       </c>
       <c r="Q46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -10816,7 +6782,7 @@
         <v>263</v>
       </c>
       <c r="Q47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="2:17">
@@ -10847,7 +6813,7 @@
         <v>238</v>
       </c>
       <c r="Q48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -10878,7 +6844,7 @@
         <v>239</v>
       </c>
       <c r="Q49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="2:17">
@@ -10909,7 +6875,7 @@
         <v>230</v>
       </c>
       <c r="Q50" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -10940,7 +6906,7 @@
         <v>231</v>
       </c>
       <c r="Q51" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -10971,7 +6937,7 @@
         <v>232</v>
       </c>
       <c r="Q52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="2:17">
@@ -11002,7 +6968,7 @@
         <v>233</v>
       </c>
       <c r="Q53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="2:17">
@@ -11033,7 +6999,7 @@
         <v>234</v>
       </c>
       <c r="Q54" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -11064,7 +7030,7 @@
         <v>235</v>
       </c>
       <c r="Q55" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="2:17">
@@ -11095,7 +7061,7 @@
         <v>236</v>
       </c>
       <c r="Q56" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="57" spans="2:17">
@@ -11126,7 +7092,7 @@
         <v>237</v>
       </c>
       <c r="Q57" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -11157,7 +7123,7 @@
         <v>263</v>
       </c>
       <c r="Q58" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="2:17">
@@ -11188,7 +7154,7 @@
         <v>238</v>
       </c>
       <c r="Q59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="2:17">
@@ -11219,7 +7185,7 @@
         <v>239</v>
       </c>
       <c r="Q60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -11232,7 +7198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:U15"/>
@@ -11456,7 +7422,7 @@
         <v>117</v>
       </c>
       <c r="K9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N9" t="s">
         <v>82</v>
@@ -11538,13 +7504,13 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K14" t="s">
+        <v>292</v>
+      </c>
+      <c r="N14" t="s">
         <v>293</v>
-      </c>
-      <c r="N14" t="s">
-        <v>294</v>
       </c>
       <c r="Q14" t="s">
         <v>50</v>
@@ -11552,13 +7518,13 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="K15" t="s">
         <v>292</v>
       </c>
-      <c r="K15" t="s">
-        <v>293</v>
-      </c>
       <c r="N15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q15" t="s">
         <v>50</v>
@@ -11573,7 +7539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
   <dimension ref="C1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -11653,6 +7619,4040 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297FE9BD-F357-45F8-8B76-EC0D919201F1}">
+  <dimension ref="B9:D191"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C10" t="s">
+        <v>481</v>
+      </c>
+      <c r="D10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11">
+        <v>47.544890908098111</v>
+      </c>
+      <c r="D11">
+        <v>7.9712762161849238</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12">
+        <v>47.304724827935445</v>
+      </c>
+      <c r="D12">
+        <v>7.7779031530618461</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13">
+        <v>47.190849773284448</v>
+      </c>
+      <c r="D13">
+        <v>8.98591839231268</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14">
+        <v>47.178826311182746</v>
+      </c>
+      <c r="D14">
+        <v>8.9144143549561985</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15">
+        <v>47.092480331016233</v>
+      </c>
+      <c r="D15">
+        <v>7.6486786287370201</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16">
+        <v>47.075251392097968</v>
+      </c>
+      <c r="D16">
+        <v>8.2262357999999978</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17">
+        <v>46.998666392047838</v>
+      </c>
+      <c r="D17">
+        <v>9.1028854000000017</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18">
+        <v>46.948264900775179</v>
+      </c>
+      <c r="D18">
+        <v>9.4806532222174642</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19">
+        <v>46.881453574552602</v>
+      </c>
+      <c r="D19">
+        <v>8.9862021733683619</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20">
+        <v>46.810115191923131</v>
+      </c>
+      <c r="D20">
+        <v>8.0932617000000064</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21">
+        <v>47.539986892396122</v>
+      </c>
+      <c r="D21">
+        <v>7.9955895999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22">
+        <v>46.788975991909084</v>
+      </c>
+      <c r="D22">
+        <v>8.1290422999999965</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23">
+        <v>46.786285291907262</v>
+      </c>
+      <c r="D23">
+        <v>9.4018789000000034</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24">
+        <v>46.664480125407628</v>
+      </c>
+      <c r="D24">
+        <v>9.5632429943814046</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25">
+        <v>46.655434346966651</v>
+      </c>
+      <c r="D25">
+        <v>8.5931628753479483</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26">
+        <v>46.649952591815854</v>
+      </c>
+      <c r="D26">
+        <v>8.5784506999999994</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27">
+        <v>46.644906911551253</v>
+      </c>
+      <c r="D27">
+        <v>8.3005733260132732</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28">
+        <v>46.623454943499027</v>
+      </c>
+      <c r="D28">
+        <v>8.5532759599539414</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29">
+        <v>46.618279365377013</v>
+      </c>
+      <c r="D29">
+        <v>8.3074651919389026</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30">
+        <v>46.612461191790615</v>
+      </c>
+      <c r="D30">
+        <v>8.5613045000000074</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31">
+        <v>46.581937628506168</v>
+      </c>
+      <c r="D31">
+        <v>9.6114226583534901</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32">
+        <v>47.446856248318333</v>
+      </c>
+      <c r="D32">
+        <v>8.7203907336648729</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
+        <v>320</v>
+      </c>
+      <c r="C33">
+        <v>46.568629391760908</v>
+      </c>
+      <c r="D33">
+        <v>9.9176659999999917</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34">
+        <v>46.56229679175663</v>
+      </c>
+      <c r="D34">
+        <v>6.5602429000000066</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35">
+        <v>46.534677991737887</v>
+      </c>
+      <c r="D35">
+        <v>8.9442773999999901</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>323</v>
+      </c>
+      <c r="C36">
+        <v>46.526125791732063</v>
+      </c>
+      <c r="D36">
+        <v>9.8856431000000047</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>324</v>
+      </c>
+      <c r="C37">
+        <v>46.497898379860622</v>
+      </c>
+      <c r="D37">
+        <v>8.3151001429309765</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>325</v>
+      </c>
+      <c r="C38">
+        <v>46.488751691706611</v>
+      </c>
+      <c r="D38">
+        <v>8.4733173999999973</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>326</v>
+      </c>
+      <c r="C39">
+        <v>46.484022953389079</v>
+      </c>
+      <c r="D39">
+        <v>8.345911817931027</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>327</v>
+      </c>
+      <c r="C40">
+        <v>46.48232639170228</v>
+      </c>
+      <c r="D40">
+        <v>9.9156705000000098</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C41">
+        <v>46.477333091698902</v>
+      </c>
+      <c r="D41">
+        <v>8.4126624000000021</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>329</v>
+      </c>
+      <c r="C42">
+        <v>46.473546691696313</v>
+      </c>
+      <c r="D42">
+        <v>8.3779117000000021</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
+        <v>330</v>
+      </c>
+      <c r="C43">
+        <v>47.434850092329576</v>
+      </c>
+      <c r="D43">
+        <v>9.4308717000000009</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>331</v>
+      </c>
+      <c r="C44">
+        <v>46.461142191687813</v>
+      </c>
+      <c r="D44">
+        <v>8.4521007999999931</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
+        <v>332</v>
+      </c>
+      <c r="C45">
+        <v>46.42086779166025</v>
+      </c>
+      <c r="D45">
+        <v>9.2172236999999928</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>333</v>
+      </c>
+      <c r="C46">
+        <v>46.410782691653388</v>
+      </c>
+      <c r="D46">
+        <v>8.6464327000000054</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
+        <v>334</v>
+      </c>
+      <c r="C47">
+        <v>46.379313191631766</v>
+      </c>
+      <c r="D47">
+        <v>7.2856905999999926</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
+        <v>335</v>
+      </c>
+      <c r="C48">
+        <v>46.352076391613046</v>
+      </c>
+      <c r="D48">
+        <v>7.2952704999999991</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" t="s">
+        <v>336</v>
+      </c>
+      <c r="C49">
+        <v>46.335742191601824</v>
+      </c>
+      <c r="D49">
+        <v>9.515274700000008</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" t="s">
+        <v>337</v>
+      </c>
+      <c r="C50">
+        <v>46.332593945141092</v>
+      </c>
+      <c r="D50">
+        <v>8.0099601184858678</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" t="s">
+        <v>338</v>
+      </c>
+      <c r="C51">
+        <v>46.300225691577296</v>
+      </c>
+      <c r="D51">
+        <v>7.9090832000000049</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" t="s">
+        <v>339</v>
+      </c>
+      <c r="C52">
+        <v>46.265255891553082</v>
+      </c>
+      <c r="D52">
+        <v>6.8250681999999925</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" t="s">
+        <v>340</v>
+      </c>
+      <c r="C53">
+        <v>46.258617991548483</v>
+      </c>
+      <c r="D53">
+        <v>6.8503240000000041</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" t="s">
+        <v>341</v>
+      </c>
+      <c r="C54">
+        <v>47.417551492318573</v>
+      </c>
+      <c r="D54">
+        <v>8.3560802000000063</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" t="s">
+        <v>342</v>
+      </c>
+      <c r="C55">
+        <v>46.242902191537631</v>
+      </c>
+      <c r="D55">
+        <v>9.0158809000000044</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" t="s">
+        <v>343</v>
+      </c>
+      <c r="C56">
+        <v>46.238390468466378</v>
+      </c>
+      <c r="D56">
+        <v>6.0514922014978874</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" t="s">
+        <v>344</v>
+      </c>
+      <c r="C57">
+        <v>46.235914155009169</v>
+      </c>
+      <c r="D57">
+        <v>6.1174054082285867</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58">
+        <v>46.224393391524778</v>
+      </c>
+      <c r="D58">
+        <v>6.9826246999999961</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59">
+        <v>46.194148141506382</v>
+      </c>
+      <c r="D59">
+        <v>8.8493960000010343</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" t="s">
+        <v>347</v>
+      </c>
+      <c r="C60">
+        <v>46.186124268919009</v>
+      </c>
+      <c r="D60">
+        <v>5.994340131372339</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61">
+        <v>46.173823141643673</v>
+      </c>
+      <c r="D61">
+        <v>8.8978103000914679</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" t="s">
+        <v>349</v>
+      </c>
+      <c r="C62">
+        <v>46.132986991479271</v>
+      </c>
+      <c r="D62">
+        <v>8.718542699932085</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" t="s">
+        <v>350</v>
+      </c>
+      <c r="C63">
+        <v>47.388461918063442</v>
+      </c>
+      <c r="D63">
+        <v>8.7320753615603035</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" t="s">
+        <v>351</v>
+      </c>
+      <c r="C64">
+        <v>46.119367580527111</v>
+      </c>
+      <c r="D64">
+        <v>7.0694412517776462</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65">
+        <v>47.346106146249483</v>
+      </c>
+      <c r="D65">
+        <v>8.0436238635106729</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" t="s">
+        <v>353</v>
+      </c>
+      <c r="C66">
+        <v>47.328602392261772</v>
+      </c>
+      <c r="D66">
+        <v>9.5426184000000038</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67">
+        <v>46.974388444635309</v>
+      </c>
+      <c r="D67">
+        <v>7.1904948515457114</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" t="s">
+        <v>355</v>
+      </c>
+      <c r="C68">
+        <v>46.804956344676071</v>
+      </c>
+      <c r="D68">
+        <v>10.332156238823757</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>356</v>
+      </c>
+      <c r="C69">
+        <v>47.412318641275661</v>
+      </c>
+      <c r="D69">
+        <v>8.5715564719984449</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" t="s">
+        <v>357</v>
+      </c>
+      <c r="C70">
+        <v>46.675294830039618</v>
+      </c>
+      <c r="D70">
+        <v>8.7674518660095799</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71">
+        <v>47.271158280917277</v>
+      </c>
+      <c r="D71">
+        <v>8.4332838059847646</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" t="s">
+        <v>359</v>
+      </c>
+      <c r="C72">
+        <v>46.592025463687065</v>
+      </c>
+      <c r="D72">
+        <v>8.3231337258397549</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73">
+        <v>47.520027177779937</v>
+      </c>
+      <c r="D73">
+        <v>7.6725301685729344</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" t="s">
+        <v>361</v>
+      </c>
+      <c r="C74">
+        <v>46.410514012428273</v>
+      </c>
+      <c r="D74">
+        <v>8.5287472013709298</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" t="s">
+        <v>362</v>
+      </c>
+      <c r="C75">
+        <v>46.972086567773282</v>
+      </c>
+      <c r="D75">
+        <v>7.282299486401616</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" t="s">
+        <v>363</v>
+      </c>
+      <c r="C76">
+        <v>46.557357312705733</v>
+      </c>
+      <c r="D76">
+        <v>6.6139061630111931</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77">
+        <v>47.378758073068163</v>
+      </c>
+      <c r="D77">
+        <v>8.6247814788577859</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78">
+        <v>46.590136747583571</v>
+      </c>
+      <c r="D78">
+        <v>9.4208498140633523</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" t="s">
+        <v>366</v>
+      </c>
+      <c r="C79">
+        <v>46.766603972636261</v>
+      </c>
+      <c r="D79">
+        <v>7.1256953875579114</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" t="s">
+        <v>367</v>
+      </c>
+      <c r="C80">
+        <v>47.337522798960869</v>
+      </c>
+      <c r="D80">
+        <v>7.2588732640160751</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" t="s">
+        <v>368</v>
+      </c>
+      <c r="C81">
+        <v>47.436744661689957</v>
+      </c>
+      <c r="D81">
+        <v>8.2162002170923429</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" t="s">
+        <v>369</v>
+      </c>
+      <c r="C82">
+        <v>46.667290772141591</v>
+      </c>
+      <c r="D82">
+        <v>8.58387184139076</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" t="s">
+        <v>370</v>
+      </c>
+      <c r="C83">
+        <v>46.366800843099547</v>
+      </c>
+      <c r="D83">
+        <v>6.1959931237841124</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" t="s">
+        <v>371</v>
+      </c>
+      <c r="C84">
+        <v>46.35035364659204</v>
+      </c>
+      <c r="D84">
+        <v>8.5954343817427024</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" t="s">
+        <v>372</v>
+      </c>
+      <c r="C85">
+        <v>46.770135591197366</v>
+      </c>
+      <c r="D85">
+        <v>8.6679070270868852</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86">
+        <v>47.185453772379887</v>
+      </c>
+      <c r="D86">
+        <v>8.1207667742378131</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" t="s">
+        <v>374</v>
+      </c>
+      <c r="C87">
+        <v>47.23246302223221</v>
+      </c>
+      <c r="D87">
+        <v>7.6158921048685695</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" t="s">
+        <v>375</v>
+      </c>
+      <c r="C88">
+        <v>47.466610199741339</v>
+      </c>
+      <c r="D88">
+        <v>8.6524389852250962</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" t="s">
+        <v>376</v>
+      </c>
+      <c r="C89">
+        <v>47.422793373651899</v>
+      </c>
+      <c r="D89">
+        <v>8.5552286743996788</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" t="s">
+        <v>377</v>
+      </c>
+      <c r="C90">
+        <v>46.822356911553562</v>
+      </c>
+      <c r="D90">
+        <v>8.1738143462569646</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" t="s">
+        <v>378</v>
+      </c>
+      <c r="C91">
+        <v>46.949503324895758</v>
+      </c>
+      <c r="D91">
+        <v>7.1526297591744381</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" t="s">
+        <v>379</v>
+      </c>
+      <c r="C92">
+        <v>47.174970614196077</v>
+      </c>
+      <c r="D92">
+        <v>7.5753719705379048</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" t="s">
+        <v>380</v>
+      </c>
+      <c r="C93">
+        <v>47.426405935677117</v>
+      </c>
+      <c r="D93">
+        <v>8.2183855607953387</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" t="s">
+        <v>381</v>
+      </c>
+      <c r="C94">
+        <v>46.191060824589286</v>
+      </c>
+      <c r="D94">
+        <v>6.0263528951053331</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" t="s">
+        <v>382</v>
+      </c>
+      <c r="C95">
+        <v>47.317528275969032</v>
+      </c>
+      <c r="D95">
+        <v>7.9466109226610806</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" t="s">
+        <v>383</v>
+      </c>
+      <c r="C96">
+        <v>47.220028502558506</v>
+      </c>
+      <c r="D96">
+        <v>8.9741608765490568</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" t="s">
+        <v>384</v>
+      </c>
+      <c r="C97">
+        <v>46.611103814178406</v>
+      </c>
+      <c r="D97">
+        <v>7.1119095241485661</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" t="s">
+        <v>385</v>
+      </c>
+      <c r="C98">
+        <v>46.34885054673623</v>
+      </c>
+      <c r="D98">
+        <v>10.062555293517526</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" t="s">
+        <v>386</v>
+      </c>
+      <c r="C99">
+        <v>46.704671298611736</v>
+      </c>
+      <c r="D99">
+        <v>9.4671012537392354</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" t="s">
+        <v>387</v>
+      </c>
+      <c r="C100">
+        <v>46.669437648312751</v>
+      </c>
+      <c r="D100">
+        <v>9.6896555979430463</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" t="s">
+        <v>388</v>
+      </c>
+      <c r="C101">
+        <v>46.670304209093366</v>
+      </c>
+      <c r="D101">
+        <v>7.8586620471824489</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" t="s">
+        <v>389</v>
+      </c>
+      <c r="C102">
+        <v>46.751315983062611</v>
+      </c>
+      <c r="D102">
+        <v>9.0427987835648143</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" t="s">
+        <v>390</v>
+      </c>
+      <c r="C103">
+        <v>46.977408013673561</v>
+      </c>
+      <c r="D103">
+        <v>9.5391741699870458</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" t="s">
+        <v>391</v>
+      </c>
+      <c r="C104">
+        <v>46.530313679899571</v>
+      </c>
+      <c r="D104">
+        <v>9.4339157546528778</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" t="s">
+        <v>392</v>
+      </c>
+      <c r="C105">
+        <v>46.287036690944227</v>
+      </c>
+      <c r="D105">
+        <v>7.5577983541354428</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" t="s">
+        <v>393</v>
+      </c>
+      <c r="C106">
+        <v>46.083826692351948</v>
+      </c>
+      <c r="D106">
+        <v>7.956552648739204</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" t="s">
+        <v>394</v>
+      </c>
+      <c r="C107">
+        <v>47.480988674223049</v>
+      </c>
+      <c r="D107">
+        <v>8.705750623710184</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" t="s">
+        <v>395</v>
+      </c>
+      <c r="C108">
+        <v>46.756029375970002</v>
+      </c>
+      <c r="D108">
+        <v>6.5540699286344619</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" t="s">
+        <v>396</v>
+      </c>
+      <c r="C109">
+        <v>46.185370247486951</v>
+      </c>
+      <c r="D109">
+        <v>7.2493006931109596</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" t="s">
+        <v>397</v>
+      </c>
+      <c r="C110">
+        <v>46.23792888408876</v>
+      </c>
+      <c r="D110">
+        <v>7.8746708803832934</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" t="s">
+        <v>398</v>
+      </c>
+      <c r="C111">
+        <v>46.066166211545358</v>
+      </c>
+      <c r="D111">
+        <v>6.9015998074716354</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" t="s">
+        <v>399</v>
+      </c>
+      <c r="C112">
+        <v>46.249132718394094</v>
+      </c>
+      <c r="D112">
+        <v>6.1334444282890637</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" t="s">
+        <v>400</v>
+      </c>
+      <c r="C113">
+        <v>47.330633116676246</v>
+      </c>
+      <c r="D113">
+        <v>8.7565727921394849</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" t="s">
+        <v>401</v>
+      </c>
+      <c r="C114">
+        <v>46.702305741170029</v>
+      </c>
+      <c r="D114">
+        <v>8.2346739749028277</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" t="s">
+        <v>402</v>
+      </c>
+      <c r="C115">
+        <v>47.111263596162431</v>
+      </c>
+      <c r="D115">
+        <v>7.9702987999010633</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" t="s">
+        <v>403</v>
+      </c>
+      <c r="C116">
+        <v>46.050896100089638</v>
+      </c>
+      <c r="D116">
+        <v>6.949838605733583</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" t="s">
+        <v>404</v>
+      </c>
+      <c r="C117">
+        <v>46.778607821978291</v>
+      </c>
+      <c r="D117">
+        <v>7.5141567559463658</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" t="s">
+        <v>405</v>
+      </c>
+      <c r="C118">
+        <v>47.559810348453667</v>
+      </c>
+      <c r="D118">
+        <v>9.0926775269382958</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" t="s">
+        <v>406</v>
+      </c>
+      <c r="C119">
+        <v>47.573740583075264</v>
+      </c>
+      <c r="D119">
+        <v>8.4736401094130844</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" t="s">
+        <v>407</v>
+      </c>
+      <c r="C120">
+        <v>47.503332863504447</v>
+      </c>
+      <c r="D120">
+        <v>7.5770135285257956</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" t="s">
+        <v>408</v>
+      </c>
+      <c r="C121">
+        <v>47.192525806627415</v>
+      </c>
+      <c r="D121">
+        <v>8.5025953004376724</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" t="s">
+        <v>409</v>
+      </c>
+      <c r="C122">
+        <v>46.197778440184173</v>
+      </c>
+      <c r="D122">
+        <v>8.7492453882474219</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" t="s">
+        <v>410</v>
+      </c>
+      <c r="C123">
+        <v>46.333583205772456</v>
+      </c>
+      <c r="D123">
+        <v>8.9793979537338995</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" t="s">
+        <v>411</v>
+      </c>
+      <c r="C124">
+        <v>46.340257020596965</v>
+      </c>
+      <c r="D124">
+        <v>9.2127758729274198</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" t="s">
+        <v>412</v>
+      </c>
+      <c r="C125">
+        <v>47.497542653552287</v>
+      </c>
+      <c r="D125">
+        <v>8.9315918186612357</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" t="s">
+        <v>413</v>
+      </c>
+      <c r="C126">
+        <v>46.162021135169752</v>
+      </c>
+      <c r="D126">
+        <v>8.9122525816708951</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" t="s">
+        <v>414</v>
+      </c>
+      <c r="C127">
+        <v>46.411435336637261</v>
+      </c>
+      <c r="D127">
+        <v>8.6126265598333376</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" t="s">
+        <v>415</v>
+      </c>
+      <c r="C128">
+        <v>47.472181885969455</v>
+      </c>
+      <c r="D128">
+        <v>7.862020493690677</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" t="s">
+        <v>416</v>
+      </c>
+      <c r="C129">
+        <v>47.452839734944206</v>
+      </c>
+      <c r="D129">
+        <v>8.4518037652382549</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" t="s">
+        <v>417</v>
+      </c>
+      <c r="C130">
+        <v>47.378105927066514</v>
+      </c>
+      <c r="D130">
+        <v>8.2848809002281207</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" t="s">
+        <v>418</v>
+      </c>
+      <c r="C131">
+        <v>47.115092797975542</v>
+      </c>
+      <c r="D131">
+        <v>8.3367437842075223</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" t="s">
+        <v>419</v>
+      </c>
+      <c r="C132">
+        <v>46.028484492512405</v>
+      </c>
+      <c r="D132">
+        <v>8.9205901102955742</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" t="s">
+        <v>420</v>
+      </c>
+      <c r="C133">
+        <v>47.365499855192191</v>
+      </c>
+      <c r="D133">
+        <v>7.9731469676031752</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" t="s">
+        <v>421</v>
+      </c>
+      <c r="C134">
+        <v>47.598960217274261</v>
+      </c>
+      <c r="D134">
+        <v>8.1833885380782423</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" t="s">
+        <v>422</v>
+      </c>
+      <c r="C135">
+        <v>46.765219065594323</v>
+      </c>
+      <c r="D135">
+        <v>9.4186944777386383</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" t="s">
+        <v>423</v>
+      </c>
+      <c r="C136">
+        <v>46.395764934452949</v>
+      </c>
+      <c r="D136">
+        <v>8.1308582732979851</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" t="s">
+        <v>424</v>
+      </c>
+      <c r="C137">
+        <v>46.774712160461192</v>
+      </c>
+      <c r="D137">
+        <v>9.1952002264269037</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" t="s">
+        <v>425</v>
+      </c>
+      <c r="C138">
+        <v>46.167302808465202</v>
+      </c>
+      <c r="D138">
+        <v>8.1183564066559004</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" t="s">
+        <v>426</v>
+      </c>
+      <c r="C139">
+        <v>46.188234494031683</v>
+      </c>
+      <c r="D139">
+        <v>8.0701490996033112</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" t="s">
+        <v>427</v>
+      </c>
+      <c r="C140">
+        <v>47.539015634556947</v>
+      </c>
+      <c r="D140">
+        <v>7.7524068439336924</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" t="s">
+        <v>428</v>
+      </c>
+      <c r="C141">
+        <v>47.154942264585237</v>
+      </c>
+      <c r="D141">
+        <v>7.7918813512983336</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" t="s">
+        <v>429</v>
+      </c>
+      <c r="C142">
+        <v>46.491577066054226</v>
+      </c>
+      <c r="D142">
+        <v>7.2732837108404942</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" t="s">
+        <v>430</v>
+      </c>
+      <c r="C143">
+        <v>46.526902581268999</v>
+      </c>
+      <c r="D143">
+        <v>8.5970130861268519</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" t="s">
+        <v>431</v>
+      </c>
+      <c r="C144">
+        <v>46.546200095956507</v>
+      </c>
+      <c r="D144">
+        <v>6.5707150506742265</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" t="s">
+        <v>432</v>
+      </c>
+      <c r="C145">
+        <v>47.302672807623779</v>
+      </c>
+      <c r="D145">
+        <v>9.5558757704346071</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" t="s">
+        <v>433</v>
+      </c>
+      <c r="C146">
+        <v>47.549929778349131</v>
+      </c>
+      <c r="D146">
+        <v>8.0505862642923702</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" t="s">
+        <v>434</v>
+      </c>
+      <c r="C147">
+        <v>47.534182026511104</v>
+      </c>
+      <c r="D147">
+        <v>8.6975363672935035</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" t="s">
+        <v>435</v>
+      </c>
+      <c r="C148">
+        <v>47.186874616216762</v>
+      </c>
+      <c r="D148">
+        <v>8.6845093233496922</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" t="s">
+        <v>436</v>
+      </c>
+      <c r="C149">
+        <v>46.541607589484336</v>
+      </c>
+      <c r="D149">
+        <v>6.4691836479843738</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" t="s">
+        <v>437</v>
+      </c>
+      <c r="C150">
+        <v>46.266170983209811</v>
+      </c>
+      <c r="D150">
+        <v>6.9744475162681168</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" t="s">
+        <v>438</v>
+      </c>
+      <c r="C151">
+        <v>46.811139511097466</v>
+      </c>
+      <c r="D151">
+        <v>9.378873087203484</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" t="s">
+        <v>439</v>
+      </c>
+      <c r="C152">
+        <v>46.680751374315896</v>
+      </c>
+      <c r="D152">
+        <v>7.6548635065014201</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" t="s">
+        <v>440</v>
+      </c>
+      <c r="C153">
+        <v>46.0317529216154</v>
+      </c>
+      <c r="D153">
+        <v>7.3084509725129267</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" t="s">
+        <v>441</v>
+      </c>
+      <c r="C154">
+        <v>46.15852172448291</v>
+      </c>
+      <c r="D154">
+        <v>7.2094009496203837</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" t="s">
+        <v>442</v>
+      </c>
+      <c r="C155">
+        <v>47.339117940297619</v>
+      </c>
+      <c r="D155">
+        <v>9.5780970318362559</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" t="s">
+        <v>443</v>
+      </c>
+      <c r="C156">
+        <v>47.657573790258297</v>
+      </c>
+      <c r="D156">
+        <v>8.7754632624143429</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" t="s">
+        <v>444</v>
+      </c>
+      <c r="C157">
+        <v>47.585912287118212</v>
+      </c>
+      <c r="D157">
+        <v>7.8435782904311289</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" t="s">
+        <v>445</v>
+      </c>
+      <c r="C158">
+        <v>47.406318762945403</v>
+      </c>
+      <c r="D158">
+        <v>8.105761472055045</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" t="s">
+        <v>446</v>
+      </c>
+      <c r="C159">
+        <v>47.427363293638969</v>
+      </c>
+      <c r="D159">
+        <v>8.3803937353034943</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" t="s">
+        <v>447</v>
+      </c>
+      <c r="C160">
+        <v>47.397732455842615</v>
+      </c>
+      <c r="D160">
+        <v>9.3025128506927892</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" t="s">
+        <v>448</v>
+      </c>
+      <c r="C161">
+        <v>47.481915935925542</v>
+      </c>
+      <c r="D161">
+        <v>9.4326555268370722</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" t="s">
+        <v>449</v>
+      </c>
+      <c r="C162">
+        <v>46.110634293306326</v>
+      </c>
+      <c r="D162">
+        <v>7.0612643589312309</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" t="s">
+        <v>450</v>
+      </c>
+      <c r="C163">
+        <v>46.44140479554256</v>
+      </c>
+      <c r="D163">
+        <v>8.8374874894540767</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" t="s">
+        <v>451</v>
+      </c>
+      <c r="C164">
+        <v>46.350910363932599</v>
+      </c>
+      <c r="D164">
+        <v>8.0409180183520075</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" t="s">
+        <v>452</v>
+      </c>
+      <c r="C165">
+        <v>47.058633982952401</v>
+      </c>
+      <c r="D165">
+        <v>8.2563745533433206</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" t="s">
+        <v>453</v>
+      </c>
+      <c r="C166">
+        <v>47.555988773696292</v>
+      </c>
+      <c r="D166">
+        <v>8.2320077689227631</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" t="s">
+        <v>454</v>
+      </c>
+      <c r="C167">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D167">
+        <v>6.289697641356212</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" t="s">
+        <v>455</v>
+      </c>
+      <c r="C168">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D168">
+        <v>6.289697641356212</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" t="s">
+        <v>456</v>
+      </c>
+      <c r="C169">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D169">
+        <v>6.289697641356212</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" t="s">
+        <v>457</v>
+      </c>
+      <c r="C170">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D170">
+        <v>6.9349650942374748</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" t="s">
+        <v>458</v>
+      </c>
+      <c r="C171">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D171">
+        <v>6.9349650942374748</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" t="s">
+        <v>459</v>
+      </c>
+      <c r="C172">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D172">
+        <v>6.9349650942374748</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" t="s">
+        <v>460</v>
+      </c>
+      <c r="C173">
+        <v>47.486990272793413</v>
+      </c>
+      <c r="D173">
+        <v>6.9349650942374748</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" t="s">
+        <v>461</v>
+      </c>
+      <c r="C174">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D174">
+        <v>7.5802325471187393</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" t="s">
+        <v>462</v>
+      </c>
+      <c r="C175">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D175">
+        <v>7.5802325471187393</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D176">
+        <v>7.5802325471187393</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" t="s">
+        <v>464</v>
+      </c>
+      <c r="C177">
+        <v>47.486990272793413</v>
+      </c>
+      <c r="D177">
+        <v>7.5802325471187393</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" t="s">
+        <v>465</v>
+      </c>
+      <c r="C178">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D178">
+        <v>8.225500000000002</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" t="s">
+        <v>466</v>
+      </c>
+      <c r="C179">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D179">
+        <v>8.225500000000002</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" t="s">
+        <v>467</v>
+      </c>
+      <c r="C180">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D180">
+        <v>8.225500000000002</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" t="s">
+        <v>468</v>
+      </c>
+      <c r="C181">
+        <v>47.486990272793413</v>
+      </c>
+      <c r="D181">
+        <v>8.225500000000002</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" t="s">
+        <v>469</v>
+      </c>
+      <c r="C182">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D182">
+        <v>8.8707674528812674</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" t="s">
+        <v>470</v>
+      </c>
+      <c r="C183">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D183">
+        <v>8.8707674528812674</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" t="s">
+        <v>471</v>
+      </c>
+      <c r="C184">
+        <v>47.486990272793413</v>
+      </c>
+      <c r="D184">
+        <v>8.8707674528812674</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" t="s">
+        <v>472</v>
+      </c>
+      <c r="C185">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D185">
+        <v>9.5160349057625293</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" t="s">
+        <v>473</v>
+      </c>
+      <c r="C186">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D186">
+        <v>9.5160349057625293</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" t="s">
+        <v>474</v>
+      </c>
+      <c r="C187">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D187">
+        <v>9.5160349057625293</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" t="s">
+        <v>475</v>
+      </c>
+      <c r="C188">
+        <v>47.486990272793413</v>
+      </c>
+      <c r="D188">
+        <v>9.5160349057625293</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" t="s">
+        <v>476</v>
+      </c>
+      <c r="C189">
+        <v>46.138009727206594</v>
+      </c>
+      <c r="D189">
+        <v>10.161302358643791</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" t="s">
+        <v>477</v>
+      </c>
+      <c r="C190">
+        <v>46.587669909068872</v>
+      </c>
+      <c r="D190">
+        <v>10.161302358643791</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" t="s">
+        <v>478</v>
+      </c>
+      <c r="C191">
+        <v>47.037330090931135</v>
+      </c>
+      <c r="D191">
+        <v>10.161302358643791</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532C3B3F-D7CF-4098-BECC-6CFBFBF7AF92}">
+  <dimension ref="B2:D184"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>297</v>
+      </c>
+      <c r="C14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" t="s">
+        <v>314</v>
+      </c>
+      <c r="D20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" t="s">
+        <v>316</v>
+      </c>
+      <c r="D22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>297</v>
+      </c>
+      <c r="C23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C24" t="s">
+        <v>318</v>
+      </c>
+      <c r="D24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" t="s">
+        <v>319</v>
+      </c>
+      <c r="D25" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>297</v>
+      </c>
+      <c r="C26" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C27" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C28" t="s">
+        <v>322</v>
+      </c>
+      <c r="D28" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" t="s">
+        <v>297</v>
+      </c>
+      <c r="C29" t="s">
+        <v>323</v>
+      </c>
+      <c r="D29" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" t="s">
+        <v>297</v>
+      </c>
+      <c r="C30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D30" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C32" t="s">
+        <v>326</v>
+      </c>
+      <c r="D32" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
+        <v>297</v>
+      </c>
+      <c r="C33" t="s">
+        <v>327</v>
+      </c>
+      <c r="D33" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" t="s">
+        <v>328</v>
+      </c>
+      <c r="D34" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>297</v>
+      </c>
+      <c r="C35" t="s">
+        <v>329</v>
+      </c>
+      <c r="D35" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>297</v>
+      </c>
+      <c r="C36" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>297</v>
+      </c>
+      <c r="C37" t="s">
+        <v>331</v>
+      </c>
+      <c r="D37" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D38" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>297</v>
+      </c>
+      <c r="C39" t="s">
+        <v>333</v>
+      </c>
+      <c r="D39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D40" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>297</v>
+      </c>
+      <c r="C41" t="s">
+        <v>335</v>
+      </c>
+      <c r="D41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C42" t="s">
+        <v>336</v>
+      </c>
+      <c r="D42" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" t="s">
+        <v>337</v>
+      </c>
+      <c r="D43" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>297</v>
+      </c>
+      <c r="C44" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
+        <v>297</v>
+      </c>
+      <c r="C45" t="s">
+        <v>339</v>
+      </c>
+      <c r="D45" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" t="s">
+        <v>340</v>
+      </c>
+      <c r="D46" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
+        <v>297</v>
+      </c>
+      <c r="C47" t="s">
+        <v>341</v>
+      </c>
+      <c r="D47" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
+        <v>297</v>
+      </c>
+      <c r="C48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" t="s">
+        <v>343</v>
+      </c>
+      <c r="D49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" t="s">
+        <v>297</v>
+      </c>
+      <c r="C50" t="s">
+        <v>344</v>
+      </c>
+      <c r="D50" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" t="s">
+        <v>297</v>
+      </c>
+      <c r="C51" t="s">
+        <v>345</v>
+      </c>
+      <c r="D51" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" t="s">
+        <v>346</v>
+      </c>
+      <c r="D52" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" t="s">
+        <v>297</v>
+      </c>
+      <c r="C53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D53" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" t="s">
+        <v>297</v>
+      </c>
+      <c r="C54" t="s">
+        <v>348</v>
+      </c>
+      <c r="D54" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" t="s">
+        <v>297</v>
+      </c>
+      <c r="C55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D55" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" t="s">
+        <v>297</v>
+      </c>
+      <c r="C56" t="s">
+        <v>350</v>
+      </c>
+      <c r="D56" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" t="s">
+        <v>297</v>
+      </c>
+      <c r="C57" t="s">
+        <v>351</v>
+      </c>
+      <c r="D57" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" t="s">
+        <v>297</v>
+      </c>
+      <c r="C58" t="s">
+        <v>352</v>
+      </c>
+      <c r="D58" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" t="s">
+        <v>297</v>
+      </c>
+      <c r="C59" t="s">
+        <v>353</v>
+      </c>
+      <c r="D59" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" t="s">
+        <v>297</v>
+      </c>
+      <c r="C60" t="s">
+        <v>354</v>
+      </c>
+      <c r="D60" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" t="s">
+        <v>355</v>
+      </c>
+      <c r="D61" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" t="s">
+        <v>297</v>
+      </c>
+      <c r="C62" t="s">
+        <v>356</v>
+      </c>
+      <c r="D62" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" t="s">
+        <v>297</v>
+      </c>
+      <c r="C63" t="s">
+        <v>357</v>
+      </c>
+      <c r="D63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" t="s">
+        <v>297</v>
+      </c>
+      <c r="C64" t="s">
+        <v>358</v>
+      </c>
+      <c r="D64" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" t="s">
+        <v>297</v>
+      </c>
+      <c r="C65" t="s">
+        <v>359</v>
+      </c>
+      <c r="D65" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" t="s">
+        <v>297</v>
+      </c>
+      <c r="C66" t="s">
+        <v>360</v>
+      </c>
+      <c r="D66" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" t="s">
+        <v>297</v>
+      </c>
+      <c r="C67" t="s">
+        <v>361</v>
+      </c>
+      <c r="D67" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" t="s">
+        <v>362</v>
+      </c>
+      <c r="D68" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>297</v>
+      </c>
+      <c r="C69" t="s">
+        <v>363</v>
+      </c>
+      <c r="D69" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" t="s">
+        <v>297</v>
+      </c>
+      <c r="C70" t="s">
+        <v>364</v>
+      </c>
+      <c r="D70" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" t="s">
+        <v>297</v>
+      </c>
+      <c r="C71" t="s">
+        <v>365</v>
+      </c>
+      <c r="D71" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" t="s">
+        <v>297</v>
+      </c>
+      <c r="C72" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>297</v>
+      </c>
+      <c r="C73" t="s">
+        <v>367</v>
+      </c>
+      <c r="D73" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" t="s">
+        <v>368</v>
+      </c>
+      <c r="D74" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" t="s">
+        <v>297</v>
+      </c>
+      <c r="C75" t="s">
+        <v>369</v>
+      </c>
+      <c r="D75" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" t="s">
+        <v>297</v>
+      </c>
+      <c r="C76" t="s">
+        <v>370</v>
+      </c>
+      <c r="D76" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" t="s">
+        <v>297</v>
+      </c>
+      <c r="C77" t="s">
+        <v>371</v>
+      </c>
+      <c r="D77" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" t="s">
+        <v>297</v>
+      </c>
+      <c r="C78" t="s">
+        <v>372</v>
+      </c>
+      <c r="D78" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" t="s">
+        <v>297</v>
+      </c>
+      <c r="C79" t="s">
+        <v>373</v>
+      </c>
+      <c r="D79" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" t="s">
+        <v>297</v>
+      </c>
+      <c r="C80" t="s">
+        <v>374</v>
+      </c>
+      <c r="D80" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" t="s">
+        <v>297</v>
+      </c>
+      <c r="C81" t="s">
+        <v>375</v>
+      </c>
+      <c r="D81" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" t="s">
+        <v>297</v>
+      </c>
+      <c r="C82" t="s">
+        <v>376</v>
+      </c>
+      <c r="D82" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" t="s">
+        <v>297</v>
+      </c>
+      <c r="C83" t="s">
+        <v>377</v>
+      </c>
+      <c r="D83" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" t="s">
+        <v>297</v>
+      </c>
+      <c r="C84" t="s">
+        <v>378</v>
+      </c>
+      <c r="D84" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" t="s">
+        <v>297</v>
+      </c>
+      <c r="C85" t="s">
+        <v>379</v>
+      </c>
+      <c r="D85" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" t="s">
+        <v>297</v>
+      </c>
+      <c r="C86" t="s">
+        <v>380</v>
+      </c>
+      <c r="D86" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" t="s">
+        <v>297</v>
+      </c>
+      <c r="C87" t="s">
+        <v>381</v>
+      </c>
+      <c r="D87" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" t="s">
+        <v>297</v>
+      </c>
+      <c r="C88" t="s">
+        <v>382</v>
+      </c>
+      <c r="D88" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" t="s">
+        <v>297</v>
+      </c>
+      <c r="C89" t="s">
+        <v>383</v>
+      </c>
+      <c r="D89" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" t="s">
+        <v>297</v>
+      </c>
+      <c r="C90" t="s">
+        <v>384</v>
+      </c>
+      <c r="D90" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" t="s">
+        <v>297</v>
+      </c>
+      <c r="C91" t="s">
+        <v>385</v>
+      </c>
+      <c r="D91" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" t="s">
+        <v>297</v>
+      </c>
+      <c r="C92" t="s">
+        <v>386</v>
+      </c>
+      <c r="D92" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" t="s">
+        <v>297</v>
+      </c>
+      <c r="C93" t="s">
+        <v>387</v>
+      </c>
+      <c r="D93" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" t="s">
+        <v>297</v>
+      </c>
+      <c r="C94" t="s">
+        <v>388</v>
+      </c>
+      <c r="D94" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" t="s">
+        <v>297</v>
+      </c>
+      <c r="C95" t="s">
+        <v>389</v>
+      </c>
+      <c r="D95" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" t="s">
+        <v>297</v>
+      </c>
+      <c r="C96" t="s">
+        <v>390</v>
+      </c>
+      <c r="D96" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" t="s">
+        <v>297</v>
+      </c>
+      <c r="C97" t="s">
+        <v>391</v>
+      </c>
+      <c r="D97" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" t="s">
+        <v>297</v>
+      </c>
+      <c r="C98" t="s">
+        <v>392</v>
+      </c>
+      <c r="D98" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" t="s">
+        <v>297</v>
+      </c>
+      <c r="C99" t="s">
+        <v>393</v>
+      </c>
+      <c r="D99" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" t="s">
+        <v>297</v>
+      </c>
+      <c r="C100" t="s">
+        <v>394</v>
+      </c>
+      <c r="D100" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>395</v>
+      </c>
+      <c r="D101" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" t="s">
+        <v>297</v>
+      </c>
+      <c r="C102" t="s">
+        <v>396</v>
+      </c>
+      <c r="D102" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" t="s">
+        <v>297</v>
+      </c>
+      <c r="C103" t="s">
+        <v>397</v>
+      </c>
+      <c r="D103" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" t="s">
+        <v>297</v>
+      </c>
+      <c r="C104" t="s">
+        <v>398</v>
+      </c>
+      <c r="D104" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" t="s">
+        <v>297</v>
+      </c>
+      <c r="C105" t="s">
+        <v>399</v>
+      </c>
+      <c r="D105" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" t="s">
+        <v>297</v>
+      </c>
+      <c r="C106" t="s">
+        <v>400</v>
+      </c>
+      <c r="D106" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" t="s">
+        <v>297</v>
+      </c>
+      <c r="C107" t="s">
+        <v>401</v>
+      </c>
+      <c r="D107" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" t="s">
+        <v>402</v>
+      </c>
+      <c r="D108" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" t="s">
+        <v>297</v>
+      </c>
+      <c r="C109" t="s">
+        <v>403</v>
+      </c>
+      <c r="D109" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" t="s">
+        <v>297</v>
+      </c>
+      <c r="C110" t="s">
+        <v>404</v>
+      </c>
+      <c r="D110" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" t="s">
+        <v>297</v>
+      </c>
+      <c r="C111" t="s">
+        <v>405</v>
+      </c>
+      <c r="D111" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" t="s">
+        <v>297</v>
+      </c>
+      <c r="C112" t="s">
+        <v>406</v>
+      </c>
+      <c r="D112" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" t="s">
+        <v>297</v>
+      </c>
+      <c r="C113" t="s">
+        <v>407</v>
+      </c>
+      <c r="D113" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" t="s">
+        <v>297</v>
+      </c>
+      <c r="C114" t="s">
+        <v>408</v>
+      </c>
+      <c r="D114" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" t="s">
+        <v>297</v>
+      </c>
+      <c r="C115" t="s">
+        <v>409</v>
+      </c>
+      <c r="D115" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" t="s">
+        <v>297</v>
+      </c>
+      <c r="C116" t="s">
+        <v>410</v>
+      </c>
+      <c r="D116" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" t="s">
+        <v>297</v>
+      </c>
+      <c r="C117" t="s">
+        <v>411</v>
+      </c>
+      <c r="D117" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" t="s">
+        <v>297</v>
+      </c>
+      <c r="C118" t="s">
+        <v>412</v>
+      </c>
+      <c r="D118" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" t="s">
+        <v>297</v>
+      </c>
+      <c r="C119" t="s">
+        <v>413</v>
+      </c>
+      <c r="D119" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" t="s">
+        <v>297</v>
+      </c>
+      <c r="C120" t="s">
+        <v>414</v>
+      </c>
+      <c r="D120" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" t="s">
+        <v>297</v>
+      </c>
+      <c r="C121" t="s">
+        <v>415</v>
+      </c>
+      <c r="D121" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" t="s">
+        <v>297</v>
+      </c>
+      <c r="C122" t="s">
+        <v>416</v>
+      </c>
+      <c r="D122" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" t="s">
+        <v>297</v>
+      </c>
+      <c r="C123" t="s">
+        <v>417</v>
+      </c>
+      <c r="D123" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" t="s">
+        <v>297</v>
+      </c>
+      <c r="C124" t="s">
+        <v>418</v>
+      </c>
+      <c r="D124" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" t="s">
+        <v>297</v>
+      </c>
+      <c r="C125" t="s">
+        <v>419</v>
+      </c>
+      <c r="D125" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" t="s">
+        <v>297</v>
+      </c>
+      <c r="C126" t="s">
+        <v>420</v>
+      </c>
+      <c r="D126" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" t="s">
+        <v>297</v>
+      </c>
+      <c r="C127" t="s">
+        <v>421</v>
+      </c>
+      <c r="D127" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" t="s">
+        <v>297</v>
+      </c>
+      <c r="C128" t="s">
+        <v>422</v>
+      </c>
+      <c r="D128" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" t="s">
+        <v>297</v>
+      </c>
+      <c r="C129" t="s">
+        <v>423</v>
+      </c>
+      <c r="D129" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" t="s">
+        <v>297</v>
+      </c>
+      <c r="C130" t="s">
+        <v>424</v>
+      </c>
+      <c r="D130" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" t="s">
+        <v>297</v>
+      </c>
+      <c r="C131" t="s">
+        <v>425</v>
+      </c>
+      <c r="D131" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" t="s">
+        <v>297</v>
+      </c>
+      <c r="C132" t="s">
+        <v>426</v>
+      </c>
+      <c r="D132" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" t="s">
+        <v>297</v>
+      </c>
+      <c r="C133" t="s">
+        <v>427</v>
+      </c>
+      <c r="D133" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" t="s">
+        <v>297</v>
+      </c>
+      <c r="C134" t="s">
+        <v>428</v>
+      </c>
+      <c r="D134" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" t="s">
+        <v>297</v>
+      </c>
+      <c r="C135" t="s">
+        <v>429</v>
+      </c>
+      <c r="D135" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" t="s">
+        <v>297</v>
+      </c>
+      <c r="C136" t="s">
+        <v>430</v>
+      </c>
+      <c r="D136" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" t="s">
+        <v>297</v>
+      </c>
+      <c r="C137" t="s">
+        <v>431</v>
+      </c>
+      <c r="D137" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" t="s">
+        <v>297</v>
+      </c>
+      <c r="C138" t="s">
+        <v>432</v>
+      </c>
+      <c r="D138" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" t="s">
+        <v>297</v>
+      </c>
+      <c r="C139" t="s">
+        <v>433</v>
+      </c>
+      <c r="D139" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" t="s">
+        <v>297</v>
+      </c>
+      <c r="C140" t="s">
+        <v>434</v>
+      </c>
+      <c r="D140" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" t="s">
+        <v>297</v>
+      </c>
+      <c r="C141" t="s">
+        <v>435</v>
+      </c>
+      <c r="D141" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" t="s">
+        <v>297</v>
+      </c>
+      <c r="C142" t="s">
+        <v>436</v>
+      </c>
+      <c r="D142" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" t="s">
+        <v>297</v>
+      </c>
+      <c r="C143" t="s">
+        <v>437</v>
+      </c>
+      <c r="D143" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" t="s">
+        <v>297</v>
+      </c>
+      <c r="C144" t="s">
+        <v>438</v>
+      </c>
+      <c r="D144" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" t="s">
+        <v>297</v>
+      </c>
+      <c r="C145" t="s">
+        <v>439</v>
+      </c>
+      <c r="D145" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" t="s">
+        <v>297</v>
+      </c>
+      <c r="C146" t="s">
+        <v>440</v>
+      </c>
+      <c r="D146" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" t="s">
+        <v>297</v>
+      </c>
+      <c r="C147" t="s">
+        <v>441</v>
+      </c>
+      <c r="D147" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" t="s">
+        <v>297</v>
+      </c>
+      <c r="C148" t="s">
+        <v>442</v>
+      </c>
+      <c r="D148" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" t="s">
+        <v>297</v>
+      </c>
+      <c r="C149" t="s">
+        <v>443</v>
+      </c>
+      <c r="D149" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" t="s">
+        <v>444</v>
+      </c>
+      <c r="D150" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" t="s">
+        <v>297</v>
+      </c>
+      <c r="C151" t="s">
+        <v>445</v>
+      </c>
+      <c r="D151" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" t="s">
+        <v>297</v>
+      </c>
+      <c r="C152" t="s">
+        <v>446</v>
+      </c>
+      <c r="D152" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" t="s">
+        <v>297</v>
+      </c>
+      <c r="C153" t="s">
+        <v>447</v>
+      </c>
+      <c r="D153" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" t="s">
+        <v>297</v>
+      </c>
+      <c r="C154" t="s">
+        <v>448</v>
+      </c>
+      <c r="D154" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" t="s">
+        <v>297</v>
+      </c>
+      <c r="C155" t="s">
+        <v>449</v>
+      </c>
+      <c r="D155" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" t="s">
+        <v>297</v>
+      </c>
+      <c r="C156" t="s">
+        <v>450</v>
+      </c>
+      <c r="D156" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" t="s">
+        <v>297</v>
+      </c>
+      <c r="C157" t="s">
+        <v>451</v>
+      </c>
+      <c r="D157" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" t="s">
+        <v>297</v>
+      </c>
+      <c r="C158" t="s">
+        <v>452</v>
+      </c>
+      <c r="D158" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" t="s">
+        <v>297</v>
+      </c>
+      <c r="C159" t="s">
+        <v>453</v>
+      </c>
+      <c r="D159" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" t="s">
+        <v>297</v>
+      </c>
+      <c r="C160" t="s">
+        <v>454</v>
+      </c>
+      <c r="D160" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" t="s">
+        <v>297</v>
+      </c>
+      <c r="C161" t="s">
+        <v>455</v>
+      </c>
+      <c r="D161" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" t="s">
+        <v>297</v>
+      </c>
+      <c r="C162" t="s">
+        <v>456</v>
+      </c>
+      <c r="D162" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" t="s">
+        <v>297</v>
+      </c>
+      <c r="C163" t="s">
+        <v>457</v>
+      </c>
+      <c r="D163" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" t="s">
+        <v>297</v>
+      </c>
+      <c r="C164" t="s">
+        <v>458</v>
+      </c>
+      <c r="D164" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" t="s">
+        <v>297</v>
+      </c>
+      <c r="C165" t="s">
+        <v>459</v>
+      </c>
+      <c r="D165" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" t="s">
+        <v>297</v>
+      </c>
+      <c r="C166" t="s">
+        <v>460</v>
+      </c>
+      <c r="D166" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" t="s">
+        <v>297</v>
+      </c>
+      <c r="C167" t="s">
+        <v>461</v>
+      </c>
+      <c r="D167" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" t="s">
+        <v>297</v>
+      </c>
+      <c r="C168" t="s">
+        <v>462</v>
+      </c>
+      <c r="D168" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" t="s">
+        <v>297</v>
+      </c>
+      <c r="C169" t="s">
+        <v>463</v>
+      </c>
+      <c r="D169" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" t="s">
+        <v>297</v>
+      </c>
+      <c r="C170" t="s">
+        <v>464</v>
+      </c>
+      <c r="D170" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" t="s">
+        <v>297</v>
+      </c>
+      <c r="C171" t="s">
+        <v>465</v>
+      </c>
+      <c r="D171" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" t="s">
+        <v>297</v>
+      </c>
+      <c r="C172" t="s">
+        <v>466</v>
+      </c>
+      <c r="D172" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" t="s">
+        <v>297</v>
+      </c>
+      <c r="C173" t="s">
+        <v>467</v>
+      </c>
+      <c r="D173" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" t="s">
+        <v>297</v>
+      </c>
+      <c r="C174" t="s">
+        <v>468</v>
+      </c>
+      <c r="D174" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" t="s">
+        <v>297</v>
+      </c>
+      <c r="C175" t="s">
+        <v>469</v>
+      </c>
+      <c r="D175" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" t="s">
+        <v>297</v>
+      </c>
+      <c r="C176" t="s">
+        <v>470</v>
+      </c>
+      <c r="D176" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" t="s">
+        <v>297</v>
+      </c>
+      <c r="C177" t="s">
+        <v>471</v>
+      </c>
+      <c r="D177" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" t="s">
+        <v>297</v>
+      </c>
+      <c r="C178" t="s">
+        <v>472</v>
+      </c>
+      <c r="D178" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" t="s">
+        <v>297</v>
+      </c>
+      <c r="C179" t="s">
+        <v>473</v>
+      </c>
+      <c r="D179" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" t="s">
+        <v>297</v>
+      </c>
+      <c r="C180" t="s">
+        <v>474</v>
+      </c>
+      <c r="D180" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" t="s">
+        <v>297</v>
+      </c>
+      <c r="C181" t="s">
+        <v>475</v>
+      </c>
+      <c r="D181" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" t="s">
+        <v>297</v>
+      </c>
+      <c r="C182" t="s">
+        <v>476</v>
+      </c>
+      <c r="D182" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" t="s">
+        <v>297</v>
+      </c>
+      <c r="C183" t="s">
+        <v>477</v>
+      </c>
+      <c r="D183" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" t="s">
+        <v>297</v>
+      </c>
+      <c r="C184" t="s">
+        <v>478</v>
+      </c>
+      <c r="D184" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D44EBE-400A-4EA2-9DA1-076783A77DFC}">
   <dimension ref="A3:S23"/>
@@ -11663,7 +11663,7 @@
   <sheetData>
     <row r="3" spans="1:19" ht="17.25" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" thickTop="1" thickBot="1">
@@ -11771,7 +11771,7 @@
     </row>
     <row r="10" spans="1:19" ht="17.25" thickBot="1">
       <c r="A10" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" thickTop="1" thickBot="1">
@@ -11838,7 +11838,7 @@
         <v>120</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -11857,7 +11857,7 @@
         <v>160</v>
       </c>
       <c r="M13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -11879,7 +11879,7 @@
         <v>160</v>
       </c>
       <c r="M14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -11890,7 +11890,7 @@
         <v>120</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -11909,7 +11909,7 @@
         <v>160</v>
       </c>
       <c r="M16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -11931,7 +11931,7 @@
         <v>160</v>
       </c>
       <c r="M17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -11942,7 +11942,7 @@
         <v>120</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -11960,7 +11960,7 @@
         <v>160</v>
       </c>
       <c r="M19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -11981,7 +11981,7 @@
         <v>160</v>
       </c>
       <c r="M20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -12001,7 +12001,7 @@
         <v>160</v>
       </c>
       <c r="M23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -12125,7 +12125,7 @@
         <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -12133,7 +12133,7 @@
         <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12666,7 +12666,7 @@
         <v>202</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -12674,7 +12674,7 @@
         <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -12691,7 +12691,7 @@
         <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:2">

--- a/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3FE111B-61E9-4B35-BEBB-358F699A353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{756201FA-8E40-4495-A8B5-18149CF1D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7620,7 +7620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297FE9BD-F357-45F8-8B76-EC0D919201F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACE3B64-9282-4696-9453-AE6DBD840B21}">
   <dimension ref="B9:D191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9637,7 +9637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532C3B3F-D7CF-4098-BECC-6CFBFBF7AF92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7D065F-590E-46B7-A4C4-B93B764C60E5}">
   <dimension ref="B2:D184"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_CHE_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{756201FA-8E40-4495-A8B5-18149CF1D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1385FB93-2A09-4918-9009-91A36D020CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7620,7 +7620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACE3B64-9282-4696-9453-AE6DBD840B21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2956C458-788B-413F-BC1B-A343B65292BD}">
   <dimension ref="B9:D191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9637,7 +9637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7D065F-590E-46B7-A4C4-B93B764C60E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE8CEA5-F12D-4C98-88D1-876BAA6D0A49}">
   <dimension ref="B2:D184"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
